--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>15144</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.7499628584162829</v>
       </c>
     </row>
     <row r="7">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>16176</v>
+        <v>1032</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.8010696776110533</v>
+        <v>0.05110681919477047</v>
       </c>
     </row>
     <row r="8">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>807</v>
+        <v>326</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.03996434407963156</v>
+        <v>0.01614420838904571</v>
       </c>
     </row>
     <row r="10">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2946</v>
+        <v>3427</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1458921408408854</v>
+        <v>0.1697122765314713</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14962,9 +14962,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15067,9 +15067,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15452,9 +15452,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15662,9 +15662,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16187,9 +16187,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16292,9 +16292,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16502,9 +16502,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16607,9 +16607,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16642,9 +16642,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16677,9 +16677,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16712,9 +16712,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16747,9 +16747,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16782,9 +16782,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16887,9 +16887,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17027,9 +17027,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17062,9 +17062,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17132,9 +17132,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17237,9 +17237,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17272,9 +17272,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17307,9 +17307,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17342,9 +17342,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17377,9 +17377,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17447,9 +17447,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17482,9 +17482,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17517,9 +17517,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17552,9 +17552,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17587,9 +17587,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17622,9 +17622,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17657,9 +17657,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17692,9 +17692,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17727,9 +17727,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17762,9 +17762,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18135,9 +18135,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18310,9 +18310,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18415,9 +18415,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18485,9 +18485,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18660,9 +18660,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18765,9 +18765,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18905,9 +18905,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19080,9 +19080,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19150,9 +19150,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19290,9 +19290,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19325,9 +19325,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19395,9 +19395,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19535,9 +19535,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20165,9 +20165,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20305,9 +20305,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20410,9 +20410,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20480,9 +20480,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20515,9 +20515,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20620,9 +20620,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21005,9 +21005,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21040,9 +21040,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21110,9 +21110,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21355,9 +21355,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21383,7 +21383,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21403,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21693,9 +21693,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21728,9 +21728,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22568,9 +22568,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22673,9 +22673,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22708,9 +22708,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22813,9 +22813,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22918,9 +22918,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23058,9 +23058,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23163,9 +23163,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23198,9 +23198,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23373,9 +23373,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23408,9 +23408,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23478,9 +23478,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23583,9 +23583,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23653,9 +23653,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23688,9 +23688,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23758,9 +23758,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23793,9 +23793,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23828,9 +23828,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23863,9 +23863,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23933,9 +23933,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23968,9 +23968,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24003,9 +24003,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24038,9 +24038,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24073,9 +24073,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24108,9 +24108,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24143,9 +24143,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24178,9 +24178,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24213,9 +24213,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24248,9 +24248,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24283,9 +24283,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24318,9 +24318,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24353,9 +24353,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24388,9 +24388,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24423,9 +24423,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24493,9 +24493,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24633,9 +24633,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24668,9 +24668,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24703,9 +24703,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24738,9 +24738,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24773,9 +24773,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24843,9 +24843,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24878,9 +24878,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24913,9 +24913,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24948,9 +24948,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24983,9 +24983,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25018,9 +25018,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25053,9 +25053,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I108" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25088,9 +25088,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I109" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25123,9 +25123,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I110" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25158,9 +25158,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I111" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25263,9 +25263,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I114" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25298,9 +25298,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I115" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25333,9 +25333,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25368,9 +25368,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I117" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -25403,9 +25403,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>$650-$1000</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>≥$1500</t>
+          <t>≥$1000</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,39 +781,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1000</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>326</v>
+        <v>3753</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.01614420838904571</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1000</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>3427</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1697122765314713</v>
+        <v>0.185856484920517</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14892,9 +14874,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15277,9 +15259,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16117,9 +16099,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16992,9 +16974,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18170,9 +18152,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18205,9 +18187,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18275,9 +18257,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18450,9 +18432,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18520,9 +18502,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18730,9 +18712,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18870,9 +18852,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18940,9 +18922,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18975,9 +18957,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19430,9 +19412,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19710,9 +19692,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19780,9 +19762,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19850,9 +19832,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19920,9 +19902,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19955,9 +19937,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20095,9 +20077,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20655,9 +20637,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20900,9 +20882,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21250,9 +21232,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21385,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21483,9 +21465,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21553,9 +21535,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21588,9 +21570,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21763,9 +21745,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22008,9 +21990,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22043,9 +22025,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23303,9 +23285,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24808,9 +24790,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17792,7 +17792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21385,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17792,7 +17792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21385,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,21 +781,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>≥$650</t>
+          <t>$650-$1500</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3753</v>
+        <v>807</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.185856484920517</v>
+        <v>0.03996434407963156</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2946</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.1458921408408854</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14874,9 +14892,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14944,9 +14962,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15049,9 +15067,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15259,9 +15277,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15434,9 +15452,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15644,9 +15662,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16099,9 +16117,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16169,9 +16187,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16484,9 +16502,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16624,9 +16642,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16974,9 +16992,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17792,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18117,9 +18135,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18152,9 +18170,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18187,9 +18205,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18257,9 +18275,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18292,9 +18310,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18397,9 +18415,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18432,9 +18450,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18467,9 +18485,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18502,9 +18520,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18642,9 +18660,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18712,9 +18730,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18747,9 +18765,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18852,9 +18870,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18887,9 +18905,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18922,9 +18940,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18957,9 +18975,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19062,9 +19080,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19132,9 +19150,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19272,9 +19290,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19307,9 +19325,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19377,9 +19395,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19412,9 +19430,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19517,9 +19535,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19692,9 +19710,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19762,9 +19780,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19832,9 +19850,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19902,9 +19920,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19937,9 +19955,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20077,9 +20095,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20147,9 +20165,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20287,9 +20305,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20392,9 +20410,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20462,9 +20480,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20497,9 +20515,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20602,9 +20620,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20637,9 +20655,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20882,9 +20900,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20987,9 +21005,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21022,9 +21040,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21092,9 +21110,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21232,9 +21250,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21337,9 +21355,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21465,9 +21483,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21535,9 +21553,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21570,9 +21588,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21675,9 +21693,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21710,9 +21728,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21745,9 +21763,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21990,9 +22008,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22025,9 +22043,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22550,9 +22568,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22690,9 +22708,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22795,9 +22813,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -23285,9 +23303,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -23355,9 +23373,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -23565,9 +23583,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -24790,9 +24808,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,39 +781,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>807</v>
+        <v>3753</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.03996434407963156</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2946</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1458921408408854</v>
+        <v>0.185856484920517</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14892,9 +14874,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14962,9 +14944,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15067,9 +15049,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15277,9 +15259,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15452,9 +15434,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15662,9 +15644,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16117,9 +16099,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16187,9 +16169,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16502,9 +16484,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16642,9 +16624,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16992,9 +16974,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17792,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18135,9 +18117,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18170,9 +18152,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18205,9 +18187,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18275,9 +18257,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18310,9 +18292,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18415,9 +18397,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18450,9 +18432,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18485,9 +18467,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18520,9 +18502,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18660,9 +18642,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18730,9 +18712,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18765,9 +18747,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18870,9 +18852,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18905,9 +18887,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18940,9 +18922,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18975,9 +18957,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19080,9 +19062,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19150,9 +19132,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19290,9 +19272,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19325,9 +19307,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19395,9 +19377,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19430,9 +19412,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19535,9 +19517,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19710,9 +19692,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19780,9 +19762,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19850,9 +19832,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19920,9 +19902,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19955,9 +19937,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20095,9 +20077,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20165,9 +20147,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20305,9 +20287,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20410,9 +20392,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20480,9 +20462,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20515,9 +20497,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20620,9 +20602,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20655,9 +20637,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20900,9 +20882,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21005,9 +20987,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21040,9 +21022,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21110,9 +21092,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21250,9 +21232,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21355,9 +21337,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21385,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21483,9 +21465,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21553,9 +21535,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21588,9 +21570,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21693,9 +21675,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21728,9 +21710,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21763,9 +21745,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22008,9 +21990,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22043,9 +22025,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22568,9 +22550,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22708,9 +22690,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22813,9 +22795,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23303,9 +23285,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23373,9 +23355,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23583,9 +23565,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24808,9 +24790,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -752,14 +752,14 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>&lt;$200</t>
+          <t>&lt;$199</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.05110681919477047</v>
+        <v>0.05100777497152478</v>
       </c>
     </row>
     <row r="8">
@@ -770,31 +770,49 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$200-$650</t>
+          <t>$200-$499</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.01307383746842965</v>
+        <v>0.008765413757242609</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>$500-$649</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.004407467934432724</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>≥$650</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>3753</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.185856484920517</v>
       </c>
     </row>
@@ -843,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1365,47 +1383,47 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Catalonia Royal Bávaro</t>
+          <t>DoubleTree by Hilton New York Times Square West</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>1958438</v>
+        <v>1886107</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>1047.54</v>
+        <v>110.5700000000002</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0.3595370392118617</v>
+        <v>0.02755729128835215</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>534.8854546327226</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
+        <v>58.62339729400305</v>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -1415,38 +1433,38 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton New York Times Square West</t>
+          <t>Dreams Macao Beach Punta Cana</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>1886107</v>
+        <v>1863573</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>110.5700000000002</v>
+        <v>-7490.62</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>0.02755729128835215</v>
+        <v>0.0106553378912444</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>58.62339729400305</v>
+        <v>0</v>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
@@ -1465,35 +1483,35 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Dreams Macao Beach Punta Cana</t>
+          <t>Hyatt Centric Times Square New York</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>1863573</v>
+        <v>1860857</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>-7490.62</v>
+        <v>-3889.240000000001</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>0.0106553378912444</v>
+        <v>0.01519407455812026</v>
       </c>
       <c r="J17" s="13" t="n">
         <v>0</v>
@@ -1515,47 +1533,47 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Centric Times Square New York</t>
+          <t>The Reef Coco Beach Resort &amp; Spa - Optional All Inclusive</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>1860857</v>
+        <v>1824525</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>-3889.240000000001</v>
+        <v>828.7099999999996</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>0.01519407455812026</v>
+        <v>0.03820720461489977</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>454.2058892040392</v>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1583,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>The Reef Coco Beach Resort &amp; Spa - Optional All Inclusive</t>
+          <t>Imperial Las Perlas</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1580,32 +1598,32 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>1824525</v>
+        <v>1816525</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>828.7099999999996</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.03820720461489977</v>
+        <v>0.02619066624461541</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>454.2058892040392</v>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1615,42 +1633,42 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Imperial Las Perlas</t>
+          <t>Riu Bambu - All Inclusive</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>1816525</v>
+        <v>1807999</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0</v>
+        <v>-2499.81</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0.02619066624461541</v>
+        <v>0.2936124411573237</v>
       </c>
       <c r="J20" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -1665,47 +1683,47 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Riu Bambu - All Inclusive</t>
+          <t>Hilton Los Angeles Airport</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>1807999</v>
+        <v>1764194</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>-2499.81</v>
+        <v>551.61</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>0.2936124411573237</v>
+        <v>0.02758880259200519</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>312.6696950562126</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1733,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Hilton Los Angeles Airport</t>
+          <t>InterContinental New York Barclay by IHG</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1730,32 +1748,32 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1764194</v>
+        <v>1723405</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>551.61</v>
+        <v>-2027.97</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>0.02758880259200519</v>
+        <v>0.04581221477249979</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>312.6696950562126</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1765,38 +1783,38 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>InterContinental New York Barclay by IHG</t>
+          <t>Beachscape Kin Ha Villas &amp; Suites Cancún</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>1723405</v>
+        <v>1706361</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>-2027.97</v>
+        <v>5.859999999999957</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0.04581221477249979</v>
+        <v>0.04550209480877727</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0</v>
+        <v>3.434208822165976</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
@@ -1815,12 +1833,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Beachscape Kin Ha Villas &amp; Suites Cancún</t>
+          <t>Dreams Sands Cancún Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1834,28 +1852,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1706361</v>
+        <v>1651676</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>5.859999999999957</v>
+        <v>451.2300000000001</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>0.04550209480877727</v>
+        <v>0.001234503619353917</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>3.434208822165976</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>273.1952271510877</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1883,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Dreams Sands Cancún Resort &amp; Spa</t>
+          <t>Aloft Cancún</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1884,28 +1902,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>1651676</v>
+        <v>1642312</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>451.2300000000001</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0.001234503619353917</v>
+        <v>0.04990038433622844</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>273.1952271510877</v>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1915,42 +1933,42 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Aloft Cancún</t>
+          <t>Hilton Copacabana Rio de Janeiro</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Marriott</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Río de Janeiro</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1642312</v>
+        <v>1618474</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0</v>
+        <v>-710.55</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0.04990038433622844</v>
+        <v>0.09786811527401738</v>
       </c>
       <c r="J26" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -1965,7 +1983,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Hilton Copacabana Rio de Janeiro</t>
+          <t>Millennium Hilton New York One UN Plaza</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1975,32 +1993,32 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Río de Janeiro</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>1618474</v>
+        <v>1603226</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>-710.55</v>
+        <v>-3062.9</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0.09786811527401738</v>
+        <v>0.02141432337050422</v>
       </c>
       <c r="J27" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -2015,35 +2033,35 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Millennium Hilton New York One UN Plaza</t>
+          <t>Cancun Bay All Inclusive Hotel</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>1603226</v>
+        <v>1585767</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>-3062.9</v>
+        <v>-4732.89</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0.02141432337050422</v>
+        <v>0.02713576458584395</v>
       </c>
       <c r="J28" s="13" t="n">
         <v>0</v>
@@ -2065,42 +2083,42 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Cancun Bay All Inclusive Hotel</t>
+          <t>Hilton New Orleans Riverside</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>1585767</v>
+        <v>1547002</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>-4732.89</v>
+        <v>128.2</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0.02713576458584395</v>
+        <v>0.0543341249720427</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>82.86996396901878</v>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2115,7 +2133,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Hilton New Orleans Riverside</t>
+          <t>Tempo by Hilton New York Times Square</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2130,32 +2148,32 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>1547002</v>
+        <v>1545854</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>128.2</v>
+        <v>419.0699999999999</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0.0543341249720427</v>
+        <v>0.07252431342157797</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>82.86996396901878</v>
+        <v>271.0928716424707</v>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2165,38 +2183,38 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Tempo by Hilton New York Times Square</t>
+          <t>Hotel Dos Playas Faranda Cancun</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>1545854</v>
+        <v>1532860</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>419.0699999999999</v>
+        <v>394.49</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0.07252431342157797</v>
+        <v>0.0516420286262281</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>271.0928716424707</v>
+        <v>257.3555314901557</v>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
@@ -2215,12 +2233,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Hotel Dos Playas Faranda Cancun</t>
+          <t>Occidental at Xcaret Destination</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2230,32 +2248,32 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>1532860</v>
+        <v>1523470</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>394.49</v>
+        <v>-720.7299999999998</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>0.0516420286262281</v>
+        <v>0.02179235560923418</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>257.3555314901557</v>
-      </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2283,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Occidental at Xcaret Destination</t>
+          <t>Iberostar Selection Cancún</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Iberostar</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2280,27 +2298,27 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>1523470</v>
+        <v>1507367</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>-720.7299999999998</v>
+        <v>0</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0.02179235560923418</v>
+        <v>0.2481903876096531</v>
       </c>
       <c r="J33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2315,42 +2333,42 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Iberostar Selection Cancún</t>
+          <t>Embassy Suites by Hilton Orlando Lake Buena Vista Resort</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Iberostar</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1507367</v>
+        <v>1494092</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0</v>
+        <v>268.76</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>0.2481903876096531</v>
+        <v>0.02459620960422785</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>179.8818278927938</v>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -2365,7 +2383,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Embassy Suites by Hilton Orlando Lake Buena Vista Resort</t>
+          <t>Hilton Orlando Buena Vista Palace - Disney Springs® Area</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2384,28 +2402,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>1494092</v>
+        <v>1474465</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>268.76</v>
+        <v>493.18</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0.02459620960422785</v>
+        <v>0.03781371548324308</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>179.8818278927938</v>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>334.4806421312137</v>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2415,12 +2433,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Hilton Orlando Buena Vista Palace - Disney Springs® Area</t>
+          <t>Hyatt Regency Miami</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2430,32 +2448,32 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>1474465</v>
+        <v>1451536</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>493.18</v>
+        <v>-2723.89</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>0.03781371548324308</v>
+        <v>0.0247992471423375</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>334.4806421312137</v>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2483,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Miami</t>
+          <t>DoubleTree by Hilton Orlando Theme Park Resort</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2480,32 +2498,32 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>1451536</v>
+        <v>1442649</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>-2723.89</v>
+        <v>288</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0.0247992471423375</v>
+        <v>0.03030050968738758</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>199.632758903933</v>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2515,42 +2533,42 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Orlando Theme Park Resort</t>
+          <t>Barceló Bávaro Palace</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>1442649</v>
+        <v>1375069</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>3</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>288</v>
+        <v>-4232.290000000001</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>0.03030050968738758</v>
+        <v>0.001757729975732127</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>199.632758903933</v>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -2565,35 +2583,35 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Barceló Bávaro Palace</t>
+          <t>All Ritmo Cancún Resort &amp; Waterpark</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>1375069</v>
+        <v>1369521</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>-4232.290000000001</v>
+        <v>-1580.84</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0.001757729975732127</v>
+        <v>0.00735366598978767</v>
       </c>
       <c r="J39" s="13" t="n">
         <v>0</v>
@@ -2615,38 +2633,38 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>All Ritmo Cancún Resort &amp; Waterpark</t>
+          <t>Hyatt Regency New Orleans</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>1369521</v>
+        <v>1326080</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>-1580.84</v>
+        <v>249.37</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>0.00735366598978767</v>
+        <v>0.02305366192084942</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>0</v>
+        <v>188.0504946911197</v>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
@@ -2665,47 +2683,47 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Solymar Beach Resort</t>
+          <t>Holiday Inn Express New York - Manhattan West Side by IHG</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>1337556</v>
+        <v>1325437</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>687.76</v>
+        <v>-1944.76</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0.04372527206337529</v>
+        <v>0.03044128087566591</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>514.1915553442249</v>
+        <v>0</v>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2715,42 +2733,42 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency New Orleans</t>
+          <t>Riu Yucatan - All Inclusive</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>1326080</v>
+        <v>1314865</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>249.37</v>
+        <v>0</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>0.02305366192084942</v>
+        <v>0.104635837139174</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>188.0504946911197</v>
-      </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -2765,12 +2783,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Express New York - Manhattan West Side by IHG</t>
+          <t>Hilton New York Fashion District</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2784,28 +2802,28 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>1325437</v>
+        <v>1314683</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>-1944.76</v>
+        <v>590.86</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0.03044128087566591</v>
+        <v>0.04806862186549914</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0</v>
+        <v>449.4315359672256</v>
       </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2815,35 +2833,35 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Riu Yucatan - All Inclusive</t>
+          <t>Hyatt Regency Grand Cypress</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1314865</v>
+        <v>1311224</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0</v>
+        <v>-467.55</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>0.104635837139174</v>
+        <v>0.09127502242179826</v>
       </c>
       <c r="J44" s="13" t="n">
         <v>0</v>
@@ -2865,47 +2883,47 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Hilton New York Fashion District</t>
+          <t>Hyatt Regency Tokyo</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1314683</v>
+        <v>1308321</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>590.86</v>
+        <v>-2661.24</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.04806862186549914</v>
+        <v>0.1700805841991377</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>449.4315359672256</v>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2915,12 +2933,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Grand Cypress</t>
+          <t>DoubleTree by Hilton Hotel Orlando Downtown</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2934,28 +2952,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>1311224</v>
+        <v>1285588</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>-467.55</v>
+        <v>321.06</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>0.09127502242179826</v>
+        <v>0.007378724754742577</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
+        <v>249.7378631412241</v>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2965,47 +2983,47 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Tokyo</t>
+          <t>Seadust Cancún Beach Resort</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>1308321</v>
+        <v>1275906</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>-2661.24</v>
+        <v>631.8599999999999</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>0.1700805841991377</v>
+        <v>0.007728625776507046</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
+        <v>495.2245698350819</v>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3033,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Thompson Central Park New York, by Hyatt</t>
+          <t>DoubleTree by Hilton Hotel Los Angeles Downtown</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3030,32 +3048,32 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1307374</v>
+        <v>1275692</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>760.23</v>
+        <v>-4224.02</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>0.005604364168172229</v>
+        <v>0.09427040382788322</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>581.4938953964206</v>
-      </c>
-      <c r="K48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3065,42 +3083,42 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Express New York City- Wall Street by IHG</t>
+          <t>Secrets Akumal Riviera Maya</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>1298880</v>
+        <v>1274310</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>735.6499999999999</v>
+        <v>528.9599999999999</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.08114991377186499</v>
+        <v>0.02065117593050357</v>
       </c>
       <c r="J49" s="13" t="n">
-        <v>566.3725671347621</v>
-      </c>
-      <c r="K49" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>415.0952280057442</v>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -3115,47 +3133,47 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Hotel Orlando Downtown</t>
+          <t>Riu Palace Bavaro - All Inclusive</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1285588</v>
+        <v>1272378</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>321.06</v>
+        <v>-3946.92</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>0.007378724754742577</v>
+        <v>0.1947840971786686</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>249.7378631412241</v>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3183,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Seadust Cancún Beach Resort</t>
+          <t>Fiesta Americana Condesa Cancún All Inclusive</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>GRUPO POSADAS</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3184,28 +3202,28 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>1275906</v>
+        <v>1266326</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>631.8599999999999</v>
+        <v>-789.16</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>0.007728625776507046</v>
+        <v>0.007714443200250174</v>
       </c>
       <c r="J51" s="13" t="n">
-        <v>495.2245698350819</v>
+        <v>0</v>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L51" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3233,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Hotel Los Angeles Downtown</t>
+          <t>Hilton Cancun Mar Caribe All-Inclusive Resort</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3225,32 +3243,32 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>1275692</v>
+        <v>1262668</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>-4224.02</v>
+        <v>-1114.19</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>0.09427040382788322</v>
+        <v>0.0006913931453081887</v>
       </c>
       <c r="J52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -3265,12 +3283,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Secrets Akumal Riviera Maya</t>
+          <t>Grand Fiesta Americana Coral Beach - All Inclusive</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>GRUPO POSADAS</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3280,32 +3298,32 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>1274310</v>
+        <v>1250670</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>528.9599999999999</v>
+        <v>-5644.34</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>0.02065117593050357</v>
+        <v>0.005080476864400681</v>
       </c>
       <c r="J53" s="13" t="n">
-        <v>415.0952280057442</v>
+        <v>0</v>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3315,47 +3333,47 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Riu Palace Bavaro - All Inclusive</t>
+          <t>Hilton Miami Downtown</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>1272378</v>
+        <v>1245306</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>-3946.92</v>
+        <v>516.28</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>0.1947840971786686</v>
+        <v>0.07836628105863137</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>0</v>
+        <v>414.5808339476401</v>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3365,42 +3383,42 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Fiesta Americana Condesa Cancún All Inclusive</t>
+          <t>Hilton Garden Inn Queens/JFK Airport</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>GRUPO POSADAS</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>1266326</v>
+        <v>1224061</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>-789.16</v>
+        <v>162.82</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>0.007714443200250174</v>
+        <v>0.03276307308214215</v>
       </c>
       <c r="J55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>133.0162467393373</v>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -3415,35 +3433,35 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Hilton Cancun Mar Caribe All-Inclusive Resort</t>
+          <t>Bahia Principe Explore Legend</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Bahia Principe</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1262668</v>
+        <v>1216228</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>-1114.19</v>
+        <v>-1349.24</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>0.0006913931453081887</v>
+        <v>0.007020887530956367</v>
       </c>
       <c r="J56" s="13" t="n">
         <v>0</v>
@@ -3465,38 +3483,38 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Grand Fiesta Americana Coral Beach - All Inclusive</t>
+          <t>Hotel Caribe By Faranda</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>GRUPO POSADAS</t>
+          <t>Faranda Hotels</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Cartagena Area</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>1250670</v>
+        <v>1210868</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>-5644.34</v>
+        <v>179.63</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>0.005080476864400681</v>
+        <v>0.001569948169412356</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>0</v>
+        <v>148.3481271286383</v>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
@@ -3515,12 +3533,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Hilton Miami Downtown</t>
+          <t>Park Central Hotel New York</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3530,32 +3548,32 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>1245306</v>
+        <v>1201294</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>516.28</v>
+        <v>0</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>0.07836628105863137</v>
+        <v>0.3415700070091085</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>414.5808339476401</v>
-      </c>
-      <c r="K58" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L58" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3565,47 +3583,47 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn Queens/JFK Airport</t>
+          <t>Wyndham Alltra Playa del Carmen Adults Only All In</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>1224061</v>
+        <v>1200963</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>162.82</v>
+        <v>585.37</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>0.03276307308214215</v>
+        <v>0.03947915131440352</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>133.0162467393373</v>
+        <v>487.4171810455443</v>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3615,42 +3633,42 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe Explore Legend</t>
+          <t>SAHARA Las Vegas</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>1216228</v>
+        <v>1200647</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>-1349.24</v>
+        <v>5.760000000000019</v>
       </c>
       <c r="I60" s="14" t="n">
-        <v>0.007020887530956367</v>
+        <v>0.03997261476520576</v>
       </c>
       <c r="J60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>4.797413394611421</v>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -3665,38 +3683,38 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Hotel Caribe By Faranda</t>
+          <t>Terracaribe Hotel Boutique</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Faranda Hotels</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Cartagena Area</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>1210868</v>
+        <v>1193135</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>179.63</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>0.001569948169412356</v>
+        <v>0.005111743432218483</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>148.3481271286383</v>
+        <v>73.30268578157542</v>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
@@ -3715,7 +3733,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Park Central Hotel New York</t>
+          <t>Hacienda Real del Caribe</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3725,37 +3743,37 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>1201294</v>
+        <v>1157394</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>0</v>
+        <v>320.84</v>
       </c>
       <c r="I62" s="14" t="n">
-        <v>0.3415700070091085</v>
+        <v>0.02520144393352653</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>277.2089711887223</v>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3783,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Wyndham Alltra Playa del Carmen Adults Only All In</t>
+          <t>Haven Riviera Cancun Resort &amp; SPA</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3784,28 +3802,28 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>1200963</v>
+        <v>1149211</v>
       </c>
       <c r="G63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>585.37</v>
+        <v>-1140.18</v>
       </c>
       <c r="I63" s="14" t="n">
-        <v>0.03947915131440352</v>
+        <v>0.04538331081063442</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>487.4171810455443</v>
+        <v>0</v>
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="L63" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3815,42 +3833,42 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>SAHARA Las Vegas</t>
+          <t>InterContinental Tokyo Bay by IHG</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>1200647</v>
+        <v>1149124</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>5.760000000000019</v>
+        <v>0</v>
       </c>
       <c r="I64" s="14" t="n">
-        <v>0.03997261476520576</v>
+        <v>0.06808403618756549</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>4.797413394611421</v>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0</v>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -3865,42 +3883,42 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Terracaribe Hotel Boutique</t>
+          <t>Pullman Paris Tour Eiffel</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>1193135</v>
+        <v>1146136</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>87.45999999999999</v>
+        <v>0</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>0.005111743432218483</v>
+        <v>0.06444610412725889</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>73.30268578157542</v>
-      </c>
-      <c r="K65" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -3915,7 +3933,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Hacienda Real del Caribe</t>
+          <t>Hotel Kavia</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -3930,23 +3948,23 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>1157394</v>
+        <v>1145081</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>320.84</v>
+        <v>254.91</v>
       </c>
       <c r="I66" s="14" t="n">
-        <v>0.02520144393352653</v>
+        <v>0.0193034379227321</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>277.2089711887223</v>
+        <v>222.6130727869906</v>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
@@ -3965,12 +3983,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Haven Riviera Cancun Resort &amp; SPA</t>
+          <t>Krystal Urban Cancun &amp; Beach Club</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Krystal</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3980,27 +3998,27 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>1149211</v>
+        <v>1141492</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>-1140.18</v>
+        <v>221.74</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>0.04538331081063442</v>
+        <v>0.004773577037771619</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>194.2545370444996</v>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4015,47 +4033,47 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>InterContinental Tokyo Bay by IHG</t>
+          <t>Hilton Los Angeles/Universal City</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1149124</v>
+        <v>1133756</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>0</v>
+        <v>228.47</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>0.06808403618756549</v>
+        <v>0.02531408874572659</v>
       </c>
       <c r="J68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="8" t="inlineStr">
+        <v>201.5160228479496</v>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4065,35 +4083,35 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Pullman Paris Tour Eiffel</t>
+          <t>Rosen Inn at Pointe Orlando</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>1146136</v>
+        <v>1132722</v>
       </c>
       <c r="G69" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H69" s="13" t="n">
-        <v>0</v>
+        <v>-445.31</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>0.06444610412725889</v>
+        <v>0.09794636283218654</v>
       </c>
       <c r="J69" s="13" t="n">
         <v>0</v>
@@ -4115,7 +4133,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Hotel Kavia</t>
+          <t>Sensira Resort &amp; Spa Riviera Maya</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -4130,32 +4148,32 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1145081</v>
+        <v>1120840</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>254.91</v>
+        <v>47.26999999999998</v>
       </c>
       <c r="I70" s="14" t="n">
-        <v>0.0193034379227321</v>
+        <v>0.008831769030370079</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>222.6130727869906</v>
+        <v>42.17372684772134</v>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4165,38 +4183,38 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Krystal Urban Cancun &amp; Beach Club</t>
+          <t>Kimpton Hotel Vintage Seattle by IHG</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Krystal</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Seattle Area</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>1141492</v>
+        <v>1119727</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H71" s="13" t="n">
-        <v>221.74</v>
+        <v>-2029.930000000001</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>0.004773577037771619</v>
+        <v>0.0059693121626968</v>
       </c>
       <c r="J71" s="13" t="n">
-        <v>194.2545370444996</v>
+        <v>0</v>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
@@ -4215,47 +4233,47 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Hilton Los Angeles/Universal City</t>
+          <t>Barcelo Maya Beach</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>1133756</v>
+        <v>1103536</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>228.47</v>
+        <v>-5985.470000000004</v>
       </c>
       <c r="I72" s="14" t="n">
-        <v>0.02531408874572659</v>
+        <v>0.08200366820837743</v>
       </c>
       <c r="J72" s="13" t="n">
-        <v>201.5160228479496</v>
-      </c>
-      <c r="K72" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4283,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Rosen Inn at Pointe Orlando</t>
+          <t>Mex Hoteles</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -4275,32 +4293,32 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>1132722</v>
+        <v>1087564</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" s="13" t="n">
-        <v>-445.31</v>
+        <v>100.96</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>0.09794636283218654</v>
+        <v>0.008050100959575712</v>
       </c>
       <c r="J73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>92.83131843275429</v>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -4315,47 +4333,47 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Washington Hilton</t>
+          <t>Sunscape Coco Punta Cana</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Greenville Area</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1129438</v>
+        <v>1084129</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>705.29</v>
+        <v>-2367.59</v>
       </c>
       <c r="I74" s="14" t="n">
-        <v>0.08513614735824365</v>
+        <v>0.02263199305617689</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>624.4610151243361</v>
-      </c>
-      <c r="K74" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4383,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Sensira Resort &amp; Spa Riviera Maya</t>
+          <t>Villa del Palmar Beach Resort and Spa Puerto Vallarta</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Villa Group</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4380,23 +4398,23 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>1120840</v>
+        <v>1076643</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" s="13" t="n">
-        <v>47.26999999999998</v>
+        <v>104.29</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>0.008831769030370079</v>
+        <v>0.01862641562709273</v>
       </c>
       <c r="J75" s="13" t="n">
-        <v>42.17372684772134</v>
+        <v>96.86590634035609</v>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
@@ -4415,42 +4433,42 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Kimpton Hotel Vintage Seattle by IHG</t>
+          <t>DoubleTree by Hilton Hotel Toronto Downtown</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Seattle Area</t>
+          <t>Toronto Area</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1119727</v>
+        <v>1066108</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>-2029.930000000001</v>
+        <v>104.8900000000001</v>
       </c>
       <c r="I76" s="14" t="n">
-        <v>0.0059693121626968</v>
+        <v>0.06303488952338787</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>98.38590461754353</v>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -4465,42 +4483,42 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Barcelo Maya Beach</t>
+          <t>The Wayfarer Downtown LA, Tapestry Collection by Hilton</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>1103536</v>
+        <v>1062663</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>-5985.470000000004</v>
+        <v>-515.8500000000001</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>0.08200366820837743</v>
+        <v>0.04337405179252501</v>
       </c>
       <c r="J77" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K77" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -4515,12 +4533,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Mex Hoteles</t>
+          <t>Las Brisas Ixtapa</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Las Brisas</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4530,23 +4548,23 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>1087564</v>
+        <v>1061537</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>100.96</v>
+        <v>-2262.47</v>
       </c>
       <c r="I78" s="14" t="n">
-        <v>0.008050100959575712</v>
+        <v>0.01625850064576176</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>92.83131843275429</v>
+        <v>0</v>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
@@ -4565,35 +4583,35 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Sunscape Coco Punta Cana</t>
+          <t>Sunset Royal Beach Resort - All Inclusive</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1084129</v>
+        <v>1058822</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H79" s="13" t="n">
-        <v>-2367.59</v>
+        <v>0</v>
       </c>
       <c r="I79" s="14" t="n">
-        <v>0.02263199305617689</v>
+        <v>0.01031712601362646</v>
       </c>
       <c r="J79" s="13" t="n">
         <v>0</v>
@@ -4615,12 +4633,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Villa del Palmar Beach Resort and Spa Puerto Vallarta</t>
+          <t>Dreams Natura Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Villa Group</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -4630,23 +4648,23 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>1076643</v>
+        <v>1057786</v>
       </c>
       <c r="G80" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>104.29</v>
+        <v>-3396.33</v>
       </c>
       <c r="I80" s="14" t="n">
-        <v>0.01862641562709273</v>
+        <v>0.003107433828770659</v>
       </c>
       <c r="J80" s="13" t="n">
-        <v>96.86590634035609</v>
+        <v>0</v>
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
@@ -4665,42 +4683,42 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Hotel Toronto Downtown</t>
+          <t>Crowne Plaza San Francisco Airport by IHG</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Toronto Area</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1066108</v>
+        <v>1053706</v>
       </c>
       <c r="G81" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>104.8900000000001</v>
+        <v>-116.91</v>
       </c>
       <c r="I81" s="14" t="n">
-        <v>0.06303488952338787</v>
+        <v>0.02061390938269309</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>98.38590461754353</v>
-      </c>
-      <c r="K81" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -4715,42 +4733,42 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>The Wayfarer Downtown LA, Tapestry Collection by Hilton</t>
+          <t>Sonesta Hotel Cartagena</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>Cartagena Area</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1062663</v>
+        <v>1052439</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>-515.8500000000001</v>
+        <v>-574.96</v>
       </c>
       <c r="I82" s="14" t="n">
-        <v>0.04337405179252501</v>
+        <v>0.02735740503725156</v>
       </c>
       <c r="J82" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K82" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -4765,42 +4783,42 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Las Brisas Ixtapa</t>
+          <t>Hilton Newark Airport</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Las Brisas</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Ixtapa / Zihuatanejo</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1061537</v>
+        <v>1050420</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>-2262.47</v>
+        <v>108.85</v>
       </c>
       <c r="I83" s="14" t="n">
-        <v>0.01625850064576176</v>
+        <v>0.03386930941908951</v>
       </c>
       <c r="J83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>103.6252165800346</v>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -4815,35 +4833,35 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Sunset Royal Beach Resort - All Inclusive</t>
+          <t>Dream Downtown, by Hyatt</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>1058822</v>
+        <v>1038378</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>0</v>
+        <v>-1531</v>
       </c>
       <c r="I84" s="14" t="n">
-        <v>0.01031712601362646</v>
+        <v>0.02442655757344628</v>
       </c>
       <c r="J84" s="13" t="n">
         <v>0</v>
@@ -4865,12 +4883,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Dreams Natura Resort &amp; Spa</t>
+          <t>Riu Palace Riviera Maya - All Inclusive</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -4884,23 +4902,23 @@
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>1057786</v>
+        <v>1026931</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85" s="13" t="n">
-        <v>-3396.33</v>
+        <v>-73.78000000000003</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>0.003107433828770659</v>
+        <v>0.2824035889460928</v>
       </c>
       <c r="J85" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -4915,12 +4933,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Crowne Plaza San Francisco Airport by IHG</t>
+          <t>Embassy Suites by Hilton Orlando International Dr Conv Ctr</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4930,27 +4948,27 @@
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>1053706</v>
+        <v>1020464</v>
       </c>
       <c r="G86" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-116.91</v>
+        <v>-156.5200000000001</v>
       </c>
       <c r="I86" s="14" t="n">
-        <v>0.02061390938269309</v>
+        <v>0.08889877545900689</v>
       </c>
       <c r="J86" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K86" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -4965,35 +4983,35 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Sonesta Hotel Cartagena</t>
+          <t>Hotel Hacienda de Castilla</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>GHL</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Cartagena Area</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>1052439</v>
+        <v>1019434</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>-574.96</v>
+        <v>-306.87</v>
       </c>
       <c r="I87" s="14" t="n">
-        <v>0.02735740503725156</v>
+        <v>0.007572829628990204</v>
       </c>
       <c r="J87" s="13" t="n">
         <v>0</v>
@@ -5015,42 +5033,42 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Hilton Newark Airport</t>
+          <t>Suites Cancun Center</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>1050420</v>
+        <v>1017569</v>
       </c>
       <c r="G88" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>108.85</v>
+        <v>172.26</v>
       </c>
       <c r="I88" s="14" t="n">
-        <v>0.03386930941908951</v>
+        <v>0.004068520169148234</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>103.6252165800346</v>
-      </c>
-      <c r="K88" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>169.28581747282</v>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -5065,35 +5083,35 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Dream Downtown, by Hyatt</t>
+          <t>Dreams Flora Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>1038378</v>
+        <v>1009069</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>-1531</v>
+        <v>-1198.77</v>
       </c>
       <c r="I89" s="14" t="n">
-        <v>0.02442655757344628</v>
+        <v>0.001678775187821645</v>
       </c>
       <c r="J89" s="13" t="n">
         <v>0</v>
@@ -5115,35 +5133,35 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Riu Palace Riviera Maya - All Inclusive</t>
+          <t>Eagle Aruba Resort</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1026931</v>
+        <v>1005712</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-73.78000000000003</v>
+        <v>-2627.65</v>
       </c>
       <c r="I90" s="14" t="n">
-        <v>0.2824035889460928</v>
+        <v>0.2414796681356094</v>
       </c>
       <c r="J90" s="13" t="n">
         <v>0</v>
@@ -5165,42 +5183,42 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Embassy Suites by Hilton Orlando International Dr Conv Ctr</t>
+          <t>Viva Azteca by Wyndham</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>1020464</v>
+        <v>1004791</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>-156.5200000000001</v>
+        <v>-235.1899999999998</v>
       </c>
       <c r="I91" s="14" t="n">
-        <v>0.08889877545900689</v>
+        <v>0.005887791590489962</v>
       </c>
       <c r="J91" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K91" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -5215,35 +5233,35 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Hotel Hacienda de Castilla</t>
+          <t>Disney's Art of Animation Resort</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>1019434</v>
+        <v>997721</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>-306.87</v>
+        <v>-4271.53</v>
       </c>
       <c r="I92" s="14" t="n">
-        <v>0.007572829628990204</v>
+        <v>0.002539788177255966</v>
       </c>
       <c r="J92" s="13" t="n">
         <v>0</v>
@@ -5265,12 +5283,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Suites Cancun Center</t>
+          <t>Dreams Jade Resort &amp; Spa – All Inclusive</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -5280,23 +5298,23 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>1017569</v>
+        <v>990548</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>172.26</v>
+        <v>-650.79</v>
       </c>
       <c r="I93" s="14" t="n">
-        <v>0.004068520169148234</v>
+        <v>0.006350020392752295</v>
       </c>
       <c r="J93" s="13" t="n">
-        <v>169.28581747282</v>
+        <v>0</v>
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
@@ -5315,35 +5333,35 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Dreams Flora Resort &amp; Spa</t>
+          <t>Hilton Cabana Miami Beach Resort</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>1009069</v>
+        <v>988110</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>-1198.77</v>
+        <v>-840.4000000000001</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>0.001678775187821645</v>
+        <v>0.01924684498689417</v>
       </c>
       <c r="J94" s="13" t="n">
         <v>0</v>
@@ -5365,42 +5383,42 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Eagle Aruba Resort</t>
+          <t>Hyatt Regency Orange County</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Anaheim Area</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1005712</v>
+        <v>984553</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>-2627.65</v>
+        <v>-1156.9</v>
       </c>
       <c r="I95" s="14" t="n">
-        <v>0.2414796681356094</v>
+        <v>0.01911933638920403</v>
       </c>
       <c r="J95" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K95" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -5415,42 +5433,42 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Viva Azteca by Wyndham</t>
+          <t>DoubleTree by Hilton Orlando Airport</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1004791</v>
+        <v>980845</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>-235.1899999999998</v>
+        <v>-158.85</v>
       </c>
       <c r="I96" s="14" t="n">
-        <v>0.005887791590489962</v>
+        <v>0.05684588288669463</v>
       </c>
       <c r="J96" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K96" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -5465,12 +5483,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn Chicago Downtown/Magnificent Mile</t>
+          <t>Hyatt Regency DFW International Airport - Adjacent to Terminal C</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -5480,32 +5498,32 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1003639</v>
+        <v>976410</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>646.24</v>
+        <v>-641.91</v>
       </c>
       <c r="I97" s="14" t="n">
-        <v>0.03753142315115295</v>
+        <v>0.01392755092635266</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>643.8968593289021</v>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L97" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5515,12 +5533,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>The Reef Playacar Beach Resort &amp; Spa - Optional All Inclusive</t>
+          <t>Riu Flamingos - All Inclusive</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -5530,32 +5548,32 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Riviera Nayarit</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1001888</v>
+        <v>966051</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>621.8699999999999</v>
+        <v>-249.9200000000001</v>
       </c>
       <c r="I98" s="14" t="n">
-        <v>0.007082627998339136</v>
+        <v>0.2207792342226238</v>
       </c>
       <c r="J98" s="13" t="n">
-        <v>620.6981219457663</v>
-      </c>
-      <c r="K98" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L98" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5565,42 +5583,42 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Disney's Art of Animation Resort</t>
+          <t>Hilton Tokyo</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>997721</v>
+        <v>957922</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>-4271.53</v>
+        <v>-3891.89</v>
       </c>
       <c r="I99" s="14" t="n">
-        <v>0.002539788177255966</v>
+        <v>0.1152546867072684</v>
       </c>
       <c r="J99" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K99" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K99" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -5615,47 +5633,47 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Residence Inn by Marriott Cancun Hotel Zone</t>
+          <t>DoubleTree by Hilton New York Midtown Fifth Ave</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>994591</v>
+        <v>940185</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H100" s="13" t="n">
-        <v>537.22</v>
+        <v>-2372.98</v>
       </c>
       <c r="I100" s="14" t="n">
-        <v>0.003292810813691256</v>
+        <v>0.05545078894047447</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>540.1416260553333</v>
-      </c>
-      <c r="K100" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K100" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5665,47 +5683,47 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Dreams Jade Resort &amp; Spa – All Inclusive</t>
+          <t>theWit Chicago, a Hilton Hotel</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>990548</v>
+        <v>938366</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H101" s="13" t="n">
-        <v>-650.79</v>
+        <v>314.06</v>
       </c>
       <c r="I101" s="14" t="n">
-        <v>0.006350020392752295</v>
+        <v>0.02799760434627853</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>0</v>
+        <v>334.6881707137727</v>
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5733,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Hilton Cabana Miami Beach Resort</t>
+          <t>Embassy Suites by Hilton Orlando Downtown</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -5730,23 +5748,23 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>988110</v>
+        <v>932778</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>-840.4000000000001</v>
+        <v>164.09</v>
       </c>
       <c r="I102" s="14" t="n">
-        <v>0.01924684498689417</v>
+        <v>0.01325824579910761</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>0</v>
+        <v>175.9153839391581</v>
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
@@ -5765,35 +5783,35 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Orange County</t>
+          <t>Hilton Barra Rio De Janeiro</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Anaheim Area</t>
+          <t>Río de Janeiro</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>984553</v>
+        <v>920723</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H103" s="13" t="n">
-        <v>-1156.9</v>
+        <v>0</v>
       </c>
       <c r="I103" s="14" t="n">
-        <v>0.01911933638920403</v>
+        <v>0.02457090786262535</v>
       </c>
       <c r="J103" s="13" t="n">
         <v>0</v>
@@ -5815,12 +5833,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Orlando Airport</t>
+          <t>Holiday Inn Express Denver Downtown by IHG</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -5830,32 +5848,32 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Denver (and vicinity), CO, US</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>980845</v>
+        <v>918457</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H104" s="13" t="n">
-        <v>-158.85</v>
+        <v>234.18</v>
       </c>
       <c r="I104" s="14" t="n">
-        <v>0.05684588288669463</v>
+        <v>0.01624463638471916</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="8" t="inlineStr">
+        <v>254.971109153722</v>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L104" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5865,35 +5883,35 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency DFW International Airport - Adjacent to Terminal C</t>
+          <t>Breathless Riviera Cancún Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>976410</v>
+        <v>913865</v>
       </c>
       <c r="G105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H105" s="13" t="n">
-        <v>-641.91</v>
+        <v>-5238.67</v>
       </c>
       <c r="I105" s="14" t="n">
-        <v>0.01392755092635266</v>
+        <v>0.008340400387365748</v>
       </c>
       <c r="J105" s="13" t="n">
         <v>0</v>
@@ -5951,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14629,9 +14647,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17792,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18782,9 +18800,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19202,9 +19220,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20567,9 +20585,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20672,9 +20690,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20777,9 +20795,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21885,9 +21903,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22585,9 +22603,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.002030406576536423</v>
+        <v>0.002265290712308079</v>
       </c>
     </row>
     <row r="7">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.0223839944535235</v>
+        <v>0.0247294236093632</v>
       </c>
     </row>
     <row r="8">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2309</v>
+        <v>2022</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1143465557371366</v>
+        <v>0.1272338283413038</v>
       </c>
     </row>
     <row r="9">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1676</v>
+        <v>1454</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.08299905907987917</v>
+        <v>0.09149257488044299</v>
       </c>
     </row>
     <row r="10">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>15715</v>
+        <v>11987</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7782399841529243</v>
+        <v>0.7542788824565819</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15144</v>
+        <v>11479</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.7499628584162829</v>
+        <v>0.7223131135162346</v>
       </c>
     </row>
     <row r="7">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1030</v>
+        <v>928</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.05100777497152478</v>
+        <v>0.0583941605839416</v>
       </c>
     </row>
     <row r="8">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.008765413757242609</v>
+        <v>0.01101182985149761</v>
       </c>
     </row>
     <row r="9">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.004407467934432724</v>
+        <v>0.005474452554744526</v>
       </c>
     </row>
     <row r="10">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3753</v>
+        <v>3223</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.185856484920517</v>
+        <v>0.2028064434935817</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14628,19 +14628,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>850169102</v>
+        <v>795463099</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2105</v>
+        <v>2019</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>470128.37</v>
+        <v>459570.19</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.02254274938352206</v>
+        <v>0.0235928103058367</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>552.9821877718628</v>
+        <v>577.7391692684918</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -14663,19 +14663,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>566365858</v>
+        <v>519694308</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6900</v>
+        <v>6048</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1112234.03</v>
+        <v>985563.8100000001</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.01643603841670837</v>
+        <v>0.01694075125410071</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1963.80840103536</v>
+        <v>1896.42987200083</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -14698,19 +14698,19 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>373644307</v>
+        <v>364408553</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2146</v>
+        <v>2120</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>594615.27</v>
+        <v>587369.34</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.05651821961253647</v>
+        <v>0.05556504597190396</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1591.393897512267</v>
+        <v>1611.842903149422</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -14733,19 +14733,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>267958206</v>
+        <v>244228195</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>24969.44</v>
+        <v>23253.56</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.08515145828375938</v>
+        <v>0.08719641890650667</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>93.18408408809842</v>
+        <v>95.21243032566325</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
@@ -14768,19 +14768,19 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>248296012</v>
+        <v>236975008</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>68513.99000000001</v>
+        <v>64107.25</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.03873001391580949</v>
+        <v>0.03927295573717208</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>275.9367315170572</v>
+        <v>270.5232528149129</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
@@ -14803,19 +14803,19 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>222428297</v>
+        <v>219850840</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1741</v>
+        <v>1701</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>461835.07</v>
+        <v>454690.88</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.02718915300601344</v>
+        <v>0.02726531770358485</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>2076.332356219946</v>
+        <v>2068.178952602592</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -14838,19 +14838,19 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>179119696</v>
+        <v>132427798</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>17127.11</v>
+        <v>16421.66</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.01816433967150101</v>
+        <v>0.02268751006491854</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>95.61823954859771</v>
+        <v>124.0046292999601</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
@@ -14873,19 +14873,19 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>140385862</v>
+        <v>119053073</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>101600.66</v>
+        <v>99664.81999999999</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.01418742579648084</v>
+        <v>0.01555516336818958</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>723.7243020953206</v>
+        <v>837.1461356566579</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -14908,19 +14908,19 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>126590432</v>
+        <v>110563038</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>14443.41</v>
+        <v>12322.37</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.02090380732723939</v>
+        <v>0.02179644340091306</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>114.0955897835944</v>
+        <v>111.4510800616749</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>52983716</v>
+        <v>52860870</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>271</v>
@@ -14952,10 +14952,10 @@
         <v>57346.7</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.02148546923360378</v>
+        <v>0.02152170405065221</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1082.345753174428</v>
+        <v>1084.861070201834</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
@@ -15048,19 +15048,19 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>26991619</v>
+        <v>25969810</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>39890.51</v>
+        <v>37185.91</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.0166399058907878</v>
+        <v>0.01637632312288769</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1477.885042760866</v>
+        <v>1431.889952217594</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>19193387</v>
+        <v>19131675</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>77</v>
@@ -15092,10 +15092,10 @@
         <v>45723.00999999999</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.02552321797085632</v>
+        <v>0.02517077046311941</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>2382.2272744253</v>
+        <v>2389.911494942288</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>18209741</v>
+        <v>18150592</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>12</v>
@@ -15127,7 +15127,7 @@
         <v>-1231.29</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.1773594143925496</v>
+        <v>0.1775613159063903</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0</v>
@@ -15258,7 +15258,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>11197452</v>
+        <v>11010823</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>36</v>
@@ -15267,14 +15267,14 @@
         <v>9475.73</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.0301122969761335</v>
+        <v>0.0297784280066985</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>846.2398409923971</v>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>860.5832643027682</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>8019485</v>
+        <v>7961476</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>28</v>
@@ -15442,10 +15442,10 @@
         <v>8538.660000000002</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.03841156882268625</v>
+        <v>0.03867235170965785</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>1064.739194599155</v>
+        <v>1072.497109832398</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
@@ -15534,23 +15534,23 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>GHL</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>7408991</v>
+        <v>7367457</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>13539.54</v>
+        <v>15094.96</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.01711947011408166</v>
+        <v>0.00844022571153113</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1827.447219196244</v>
+        <v>2048.86977962681</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
@@ -15569,23 +15569,23 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>7367457</v>
+        <v>7169041</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>15094.96</v>
+        <v>13317.49</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.00844022571153113</v>
+        <v>0.01695945106186448</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>2048.86977962681</v>
+        <v>1857.638978490987</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>6415276</v>
+        <v>6357971</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>197</v>
@@ -15687,10 +15687,10 @@
         <v>196268.13</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.03444886860674427</v>
+        <v>0.03469298617436285</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>30593.87156530756</v>
+        <v>30869.61705235837</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>5930465</v>
+        <v>5871017</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>81</v>
@@ -15792,10 +15792,10 @@
         <v>19225.02</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.04553892485665121</v>
+        <v>0.04506374278936682</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>3241.739054188838</v>
+        <v>3274.56384473082</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>5848200</v>
+        <v>5783699</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>1</v>
@@ -15827,10 +15827,10 @@
         <v>168.05</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.1141453780650457</v>
+        <v>0.1151928895331517</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>28.73533736876304</v>
+        <v>29.0557997572142</v>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
@@ -15849,27 +15849,27 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Camino Real</t>
+          <t>Sandos</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>5716736</v>
+        <v>5695278</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>10070.5</v>
+        <v>26951.04</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.04535122839326497</v>
+        <v>0.0200848843550745</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>1761.58213358112</v>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>4732.172863203517</v>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -15884,27 +15884,27 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Sandos</t>
+          <t>Camino Real</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>5695278</v>
+        <v>5533592</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>26951.04</v>
+        <v>9927</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.0200848843550745</v>
+        <v>0.04450870248475131</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>4732.172863203517</v>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1793.952282712567</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>5451443</v>
+        <v>4958497</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>6</v>
@@ -15932,7 +15932,7 @@
         <v>-85.72</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.0375010799892799</v>
+        <v>0.0385889111156062</v>
       </c>
       <c r="G43" s="13" t="n">
         <v>0</v>
@@ -15993,19 +15993,19 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>4109357</v>
+        <v>4050942</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>-66.83000000000004</v>
+        <v>238.64</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.005875371743073186</v>
+        <v>0.005642144469113604</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0</v>
+        <v>58.90975481752145</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -16028,19 +16028,19 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>3991350</v>
+        <v>3577256</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>86.18000000000001</v>
+        <v>200.84</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.08220301401781352</v>
+        <v>0.08196897286635343</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>21.59169203402358</v>
+        <v>56.14359162441827</v>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>3328534</v>
+        <v>3270050</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>7</v>
@@ -16107,10 +16107,10 @@
         <v>3099.35</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.01318568474890147</v>
+        <v>0.01277319918655678</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>931.1456635263452</v>
+        <v>947.7989633186036</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
@@ -16129,32 +16129,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Mision</t>
+          <t>Villa Group</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>2587947</v>
+        <v>2578705</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>1242.97</v>
+        <v>3846.63</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.04541399031742149</v>
+        <v>0.01620542093802897</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>480.2919070599206</v>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1491.690596636684</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16164,32 +16164,32 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Villa Group</t>
+          <t>Mision</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>2578705</v>
+        <v>2470660</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>3846.63</v>
+        <v>847.8400000000001</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.01620542093802897</v>
+        <v>0.04405462507993815</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>1491.690596636684</v>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>343.1633652546284</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>1366070</v>
+        <v>1300304</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>1</v>
@@ -16527,10 +16527,10 @@
         <v>127.78</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.02009340663362785</v>
+        <v>0.01988765704019983</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>93.53839847152781</v>
+        <v>98.26932778796343</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1142990</v>
+        <v>1086170</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>2</v>
@@ -16632,10 +16632,10 @@
         <v>1562.34</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.005208269538666131</v>
+        <v>0.005242273308966369</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>1366.888599200343</v>
+        <v>1438.393621624608</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>978918</v>
+        <v>917017</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>0</v>
@@ -16737,7 +16737,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.09070320496711676</v>
+        <v>0.09569397295797133</v>
       </c>
       <c r="G66" s="13" t="n">
         <v>0</v>
@@ -16938,7 +16938,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>467103</v>
+        <v>355605</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>3</v>
@@ -16947,7 +16947,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>0.02559820853216528</v>
+        <v>0.01984505279734537</v>
       </c>
       <c r="G72" s="13" t="n">
         <v>0</v>
@@ -17039,32 +17039,32 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Ostar</t>
+          <t>Fontan</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>289665</v>
+        <v>261950</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>0</v>
+        <v>552.02</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.06150553225277475</v>
+        <v>0.005585035312082458</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>2107.348730673792</v>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17074,32 +17074,32 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Fontan</t>
+          <t>Ostar</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>261950</v>
+        <v>234454</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>552.02</v>
+        <v>0</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.005585035312082458</v>
+        <v>0.07158760353843398</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>2107.348730673792</v>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17109,32 +17109,32 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>DOT Hotels</t>
+          <t>Regency &amp; Santorini</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>243009</v>
+        <v>202337</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.04584192355015659</v>
+        <v>0.05134503328605248</v>
       </c>
       <c r="G77" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17144,32 +17144,32 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Grupo Welcome</t>
+          <t>Zar</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>220359</v>
+        <v>201777</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>-29.72000000000003</v>
+        <v>0</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.03494751746014459</v>
+        <v>0.002230184807981088</v>
       </c>
       <c r="G78" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17179,32 +17179,32 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Regency &amp; Santorini</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>202337</v>
+        <v>196671</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.05134503328605248</v>
+        <v>0.0009152340711136873</v>
       </c>
       <c r="G79" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17214,11 +17214,11 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Zar</t>
+          <t>Sandals</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>201777</v>
+        <v>192912</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>0</v>
@@ -17227,14 +17227,14 @@
         <v>0</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>0.002230184807981088</v>
+        <v>0.2170315999004727</v>
       </c>
       <c r="G80" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -17249,11 +17249,11 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Eurostars Hotels</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>196671</v>
+        <v>154780</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>0</v>
@@ -17262,14 +17262,14 @@
         <v>0</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>0.0009152340711136873</v>
+        <v>0.1010337252875048</v>
       </c>
       <c r="G81" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -17284,32 +17284,32 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Sandals</t>
+          <t>Grupo Welcome</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>192912</v>
+        <v>153667</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E82" s="13" t="n">
-        <v>0</v>
+        <v>-29.72000000000003</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>0.2170315999004727</v>
+        <v>0.04160945420942688</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="7" t="inlineStr">
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17319,32 +17319,32 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Prisma Hoteles</t>
+          <t>BlueBay</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>155495</v>
+        <v>141642</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>0</v>
+        <v>-855.8200000000001</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.03966043924241937</v>
+        <v>0.3121319947473207</v>
       </c>
       <c r="G83" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17354,11 +17354,11 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Eurostars Hotels</t>
+          <t>Red Roof</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>154780</v>
+        <v>123931</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>0</v>
@@ -17367,14 +17367,14 @@
         <v>0</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0.1010337252875048</v>
+        <v>0.01884919834423994</v>
       </c>
       <c r="G84" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -17389,32 +17389,32 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>BlueBay</t>
+          <t>DOT Hotels</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>141642</v>
+        <v>121835</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>-855.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>0.3121319947473207</v>
+        <v>0.03967661181105594</v>
       </c>
       <c r="G85" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17424,11 +17424,11 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Red Roof</t>
+          <t>Marival</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>123931</v>
+        <v>118279</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>0</v>
@@ -17437,7 +17437,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>0.01884919834423994</v>
+        <v>0.0002874559304694832</v>
       </c>
       <c r="G86" s="13" t="n">
         <v>0</v>
@@ -17459,11 +17459,11 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Marival</t>
+          <t>Hotusa Hotels</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>118279</v>
+        <v>101899</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>0</v>
@@ -17472,7 +17472,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.0002874559304694832</v>
+        <v>0.0102650663892678</v>
       </c>
       <c r="G87" s="13" t="n">
         <v>0</v>
@@ -17494,11 +17494,11 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Hotusa Hotels</t>
+          <t>Prisma Hoteles</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>101899</v>
+        <v>93655</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>0</v>
@@ -17507,14 +17507,14 @@
         <v>0</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>0.0102650663892678</v>
+        <v>0.04925524531525279</v>
       </c>
       <c r="G88" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -17693,76 +17693,6 @@
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>Ayenda Hoteles</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>57052</v>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="14" t="n">
-        <v>0.02075299726565239</v>
-      </c>
-      <c r="G94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Viaggio</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>55924</v>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="14" t="n">
-        <v>0.007295615478148916</v>
-      </c>
-      <c r="G95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -17787,7 +17717,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -17810,7 +17740,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17801,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>166532279</v>
+        <v>166351911</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>977</v>
@@ -17880,10 +17810,10 @@
         <v>495611.08</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.03375505958217265</v>
+        <v>0.03377356452490648</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>2976.066159522143</v>
+        <v>2979.292976081291</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -17906,7 +17836,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>157004520</v>
+        <v>156578482</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>244</v>
@@ -17915,10 +17845,10 @@
         <v>47330.78</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.04446378359043421</v>
+        <v>0.04454847761265178</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>301.461257293739</v>
+        <v>302.2815101758363</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -17941,7 +17871,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>150584573</v>
+        <v>149678003</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>296</v>
@@ -17950,10 +17880,10 @@
         <v>71787.78</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.04048481779073079</v>
+        <v>0.04059262468914687</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>476.7273205336911</v>
+        <v>479.614763433208</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
@@ -17976,19 +17906,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>141328686</v>
+        <v>141014525</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>515901</v>
+        <v>515134.09</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.04032617978207199</v>
+        <v>0.04039000946888273</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>3650.362956038521</v>
+        <v>3653.056945729526</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -18011,7 +17941,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>102087847</v>
+        <v>102029086</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>901</v>
@@ -18020,10 +17950,10 @@
         <v>526542.1</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.04493764081438607</v>
+        <v>0.04495885614421754</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>5157.735376670252</v>
+        <v>5160.705840293424</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
@@ -18046,7 +17976,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>81960475</v>
+        <v>81660350</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>57</v>
@@ -18055,7 +17985,7 @@
         <v>-16634.38</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.04477506993462398</v>
+        <v>0.04484948937887236</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>0</v>
@@ -18081,7 +18011,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>70232758</v>
+        <v>69561244</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>130</v>
@@ -18090,10 +18020,10 @@
         <v>11927.6</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.04391907833094067</v>
+        <v>0.04372278046091298</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>169.8295829419087</v>
+        <v>171.469043883114</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -18116,19 +18046,19 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>65647968</v>
+        <v>62455903</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>71397.31999999999</v>
+        <v>69878.67</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.03449300974555679</v>
+        <v>0.03568208756824795</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1087.578521851583</v>
+        <v>1118.848125532666</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -18151,7 +18081,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>59946960</v>
+        <v>57689165</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>188</v>
@@ -18160,10 +18090,10 @@
         <v>39018.77</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.03315312402830769</v>
+        <v>0.03366032425673001</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>650.8882185185035</v>
+        <v>676.3621903697166</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
@@ -18186,7 +18116,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>55601278</v>
+        <v>55352021</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>185</v>
@@ -18195,10 +18125,10 @@
         <v>45431.26</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.0353392776331508</v>
+        <v>0.03536833822201361</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>817.090211487585</v>
+        <v>820.7696698192826</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -18221,19 +18151,19 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>54463897</v>
+        <v>54228561</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>141716.14</v>
+        <v>141165.94</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.04486046967957508</v>
+        <v>0.04502732425446436</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>2602.019829759887</v>
+        <v>2603.165885224209</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
@@ -18252,27 +18182,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>46956714</v>
+        <v>45155618</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>41809.24</v>
+        <v>52867.58</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0.02293067185237877</v>
+        <v>0.04218919116553781</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>890.3783173584079</v>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1170.786323863401</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -18287,27 +18217,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>46178622</v>
+        <v>41276150</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>52867.58</v>
+        <v>41030.38</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.04180012127689735</v>
+        <v>0.02360086878257783</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1144.849666583814</v>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>994.0457140503655</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -18326,7 +18256,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>36979011</v>
+        <v>36181721</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>23</v>
@@ -18335,10 +18265,10 @@
         <v>9554.970000000001</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.07958211754229988</v>
+        <v>0.07923191381637153</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>258.3890088353093</v>
+        <v>264.0827947349437</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
@@ -18396,7 +18326,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>31973725</v>
+        <v>31237701</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>118</v>
@@ -18405,10 +18335,10 @@
         <v>41145.74</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.02418776667404252</v>
+        <v>0.02435969919809399</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1286.861008531224</v>
+        <v>1317.182080717143</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
@@ -18427,23 +18357,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Houston (and vicinity), TX, US</t>
+          <t>Cartagena Area</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>31200256</v>
+        <v>30537071</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>27490.91</v>
+        <v>31793.58</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.02215847203304998</v>
+        <v>0.01470183568031132</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>881.1116806221077</v>
+        <v>1041.147004570281</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
@@ -18462,32 +18392,32 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Cartagena Area</t>
+          <t>Dubai Area</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>30971541</v>
+        <v>29078378</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>32060.95</v>
+        <v>3045.87</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.01461025139175348</v>
+        <v>0.064505798775984</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1035.174517147855</v>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>104.7469016325464</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -18497,32 +18427,32 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Atlanta Area</t>
+          <t>Toronto Area</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>30637690</v>
+        <v>27402428</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>22059.25</v>
+        <v>11719.65</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.0258640582889898</v>
+        <v>0.0462807529318205</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>720.003694795528</v>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>427.686553906829</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -18532,32 +18462,32 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Dubai Area</t>
+          <t>Atlanta Area</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>29873290</v>
+        <v>27340771</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>3045.87</v>
+        <v>22030.09</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.06700125764520747</v>
+        <v>0.02726964064034624</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>101.9596435477981</v>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>805.7596473779031</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18567,32 +18497,32 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Toronto Area</t>
+          <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>28056673</v>
+        <v>27148304</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>11719.65</v>
+        <v>27304.04</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.04563641597847329</v>
+        <v>0.02336330107398238</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>417.7134616067985</v>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1005.736490942491</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18536,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>26953798</v>
+        <v>26377829</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>98</v>
@@ -18615,10 +18545,10 @@
         <v>12225.95</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.04526976124106889</v>
+        <v>0.04540449481267014</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>453.5891379760285</v>
+        <v>463.4934133510381</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
@@ -18637,32 +18567,32 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Nashville (and vicinity), TN, US</t>
+          <t>Anaheim Area</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>25983835</v>
+        <v>24476923</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>34150.45</v>
+        <v>6034.719999999999</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.02022091812082397</v>
+        <v>0.04348512270108461</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1314.295984407229</v>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>246.5473294988917</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -18672,32 +18602,32 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Anaheim Area</t>
+          <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>24846512</v>
+        <v>23941126</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>6034.719999999999</v>
+        <v>33296.49</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.04358825093840133</v>
+        <v>0.02145262507703272</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>242.879966411382</v>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1390.765413456326</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18707,27 +18637,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Phoenix (and vicinity), AZ, US</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>24830012</v>
+        <v>23189631</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>22263.36</v>
+        <v>36355.75</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.01567006894720792</v>
+        <v>0.03762336709885552</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>896.6310608307398</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1567.758883269854</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -18742,27 +18672,27 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Phoenix (and vicinity), AZ, US</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>24823768</v>
+        <v>22624680</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>37019.76</v>
+        <v>20108.64</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.03630746146193439</v>
+        <v>0.0164175581709885</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>1491.303012499956</v>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>888.7922392714504</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -18781,7 +18711,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>22277701</v>
+        <v>21769187</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>56</v>
@@ -18790,10 +18720,10 @@
         <v>12714.23</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.03097770277103548</v>
+        <v>0.03094759579216257</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>570.7155329896923</v>
+        <v>584.047075345533</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -18816,7 +18746,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>21873513</v>
+        <v>21628783</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>126</v>
@@ -18825,10 +18755,10 @@
         <v>70181.44</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.05363422875877322</v>
+        <v>0.05389207520367651</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>3208.512505512947</v>
+        <v>3244.81687203575</v>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
@@ -18851,19 +18781,19 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>21189133</v>
+        <v>19853961</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>13986.38</v>
+        <v>14324.94</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0.02786541572984605</v>
+        <v>0.02878287108552293</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>660.0732554748701</v>
+        <v>721.5154698853291</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
@@ -18882,27 +18812,27 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Denver (and vicinity), CO, US</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>19969786</v>
+        <v>18820079</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>22733.29</v>
+        <v>14780.06</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.02060998550510256</v>
+        <v>0.08221532970185726</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1138.384257097197</v>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>785.3346417940118</v>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -18917,32 +18847,32 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Rome Area</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>19055096</v>
+        <v>18681679</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>12895.98</v>
+        <v>8931.330000000002</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.02764494075495605</v>
+        <v>0.07951994036510315</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>676.7732894129738</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>478.0796201454913</v>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -18952,27 +18882,27 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>19004524</v>
+        <v>18304160</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>16047.44</v>
+        <v>12895.98</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.08216932978694967</v>
+        <v>0.02807951853567714</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>844.4010489291919</v>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>704.5382033373834</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -18987,32 +18917,32 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Rome Area</t>
+          <t>Denver (and vicinity), CO, US</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>18740911</v>
+        <v>17935948</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>8931.330000000002</v>
+        <v>22652.95</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.08016200493135045</v>
+        <v>0.02203017091708785</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>476.5686150475824</v>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1262.991507334878</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19026,19 +18956,19 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>17868618</v>
+        <v>16993664</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>6676.44</v>
+        <v>6251.64</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.01272924408591644</v>
+        <v>0.0128404327636465</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>373.6405356026974</v>
+        <v>367.8806406905538</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -19057,27 +18987,27 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Washington, DC Area</t>
+          <t>Riviera Nayarit</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>16507085</v>
+        <v>16067591</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>77</v>
+        <v>629</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>20744.93</v>
+        <v>306579.93</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.02829639515395965</v>
+        <v>0.04727690666261047</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1256.728853095504</v>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>19080.64065110943</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -19092,27 +19022,27 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Riviera Nayarit</t>
+          <t>Washington, DC Area</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>16134368</v>
+        <v>15547028</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>629</v>
+        <v>77</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>306579.93</v>
+        <v>20744.93</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.04714228657732364</v>
+        <v>0.02697042804579756</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>19001.66960366839</v>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1334.334124824371</v>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -19127,32 +19057,32 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Berlin Area</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>15793780</v>
+        <v>15090756</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>17919.83</v>
+        <v>9553.129999999999</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.01631673988114308</v>
+        <v>0.03838131104896269</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>1134.613119848447</v>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>633.0451569159292</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19096,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>15677795</v>
+        <v>15027656</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>88</v>
@@ -19175,10 +19105,10 @@
         <v>26599</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.03456799887994454</v>
+        <v>0.03574403087214666</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>1696.603380768788</v>
+        <v>1770.003252669611</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
@@ -19197,32 +19127,32 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Berlin Area</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>15519988</v>
+        <v>14960093</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>9553.129999999999</v>
+        <v>3040.419999999999</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.03775814775114517</v>
+        <v>0.1196620903359358</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>615.5372027349506</v>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>203.2353675876212</v>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19232,32 +19162,32 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>15142684</v>
+        <v>13699361</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>3040.419999999999</v>
+        <v>17204.87</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.1209886569646438</v>
+        <v>0.0173219028245186</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>200.7847485954273</v>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1255.888504580615</v>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19267,32 +19197,32 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>15113227</v>
+        <v>13569917</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>15703.23</v>
+        <v>3405.01</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.01808726885396481</v>
+        <v>0.09392680883751905</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>1039.038849876337</v>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>250.9234212707418</v>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19302,27 +19232,27 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Philadelphia (and vicinity), PA, US</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>14265602</v>
+        <v>13265626</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>17164.03</v>
+        <v>14539.82</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.03884876362035055</v>
+        <v>0.01998541192100546</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>1203.176003368102</v>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1096.052308424796</v>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -19337,32 +19267,32 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Philadelphia (and vicinity), PA, US</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>13632389</v>
+        <v>13158050</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>3405.01</v>
+        <v>16966.78</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.0964569012812061</v>
+        <v>0.04029396453121853</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>249.7735356583501</v>
-      </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1289.46006437124</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19372,32 +19302,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Tampa Area</t>
+          <t>London Area</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>13466902</v>
+        <v>12789935</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>17797.87</v>
+        <v>5550.690000000001</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.02609575684147698</v>
+        <v>0.01902675815006096</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>1321.600914597878</v>
+        <v>433.9889139389684</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19411,19 +19341,19 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>13204973</v>
+        <v>12725374</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>11204.37</v>
+        <v>10657.71</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.07031646335058769</v>
+        <v>0.07081237848097824</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>848.4962445587736</v>
+        <v>837.5164454891463</v>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
@@ -19442,32 +19372,32 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>London Area</t>
+          <t>Tampa Area</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>13085362</v>
+        <v>12389710</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>5550.690000000001</v>
+        <v>17653.43</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.01924234117481809</v>
+        <v>0.02785916700229465</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>424.1907866209586</v>
+        <v>1424.846102128299</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19481,19 +19411,19 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>12984636</v>
+        <v>12303787</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>21173.12</v>
+        <v>18477.81</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0.04338850931208237</v>
+        <v>0.04302455821122391</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>1630.628690708003</v>
+        <v>1501.798592579667</v>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
@@ -19516,19 +19446,19 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>12727440</v>
+        <v>12132953</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>12833.75</v>
+        <v>11226.7</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.03431287045941682</v>
+        <v>0.03470144489968766</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>1008.352818791525</v>
+        <v>925.3064773266657</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
@@ -19551,7 +19481,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>12124803</v>
+        <v>11886680</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>84</v>
@@ -19560,10 +19490,10 @@
         <v>29178.79</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.03958662256203255</v>
+        <v>0.03973010125619601</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>2406.537244357702</v>
+        <v>2454.746825858861</v>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
@@ -19582,27 +19512,27 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Río de Janeiro</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>12013267</v>
+        <v>11833213</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>-4829.14</v>
+        <v>1373.8</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.02880540322628308</v>
+        <v>0.07878097013887944</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>116.0969552394603</v>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -19617,27 +19547,27 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Río de Janeiro</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>11898938</v>
+        <v>11712827</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>1373.8</v>
+        <v>-4829.14</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0.07848650022380149</v>
+        <v>0.0282626901259619</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>115.4556818432032</v>
-      </c>
-      <c r="H56" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -19656,19 +19586,19 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>11804735</v>
+        <v>11390313</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>5360.929999999999</v>
+        <v>5232.419999999999</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.04337589958605594</v>
+        <v>0.04424724763928788</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>454.1338708577532</v>
+        <v>459.3745580125848</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
@@ -19687,27 +19617,27 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Minneapolis - St. Paul Area</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11599862</v>
+        <v>11197455</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>9253.300000000001</v>
+        <v>9338.220000000001</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.008627085391188274</v>
+        <v>0.03883239539698976</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>797.707765833766</v>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>833.9591451807577</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -19726,7 +19656,7 @@
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>11520554</v>
+        <v>11165181</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>13</v>
@@ -19735,10 +19665,10 @@
         <v>2907.54</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.05158554007038203</v>
+        <v>0.05223703941745324</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>252.3784880484046</v>
+        <v>260.4113627893717</v>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
@@ -19757,27 +19687,27 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Honolulu Area</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>11439784</v>
+        <v>11008993</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>9338.220000000001</v>
+        <v>34188.97</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.0392123662474746</v>
+        <v>0.01249996253063291</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>816.2933845604078</v>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>3105.549254141592</v>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -19792,27 +19722,27 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Honolulu Area</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>11008993</v>
+        <v>10833685</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>34188.97</v>
+        <v>37983.31</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.01249996253063291</v>
+        <v>0.07126531738738942</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>3105.549254141592</v>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>3506.037880924173</v>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -19831,7 +19761,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>10890705</v>
+        <v>10699166</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>120</v>
@@ -19840,10 +19770,10 @@
         <v>7798.24</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0.02035699249956729</v>
+        <v>0.02041663808188414</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>716.0454718037079</v>
+        <v>728.8642871790194</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
@@ -19862,27 +19792,27 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Bávaro Area</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>10889277</v>
+        <v>10001277</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>37983.31</v>
+        <v>9076.43</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.07094979767710932</v>
+        <v>0.0249126186585973</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>3488.138836031079</v>
-      </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>907.5271087882078</v>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -19897,23 +19827,23 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Bávaro Area</t>
+          <t>Minneapolis - St. Paul Area</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>10001277</v>
+        <v>9778755</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E64" s="13" t="n">
-        <v>9076.43</v>
+        <v>9082.57</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>0.0249126186585973</v>
+        <v>0.007396749381695318</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>907.5271087882078</v>
+        <v>928.806376680876</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
@@ -19936,19 +19866,19 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>9722947</v>
+        <v>9552579</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>7500.410000000001</v>
+        <v>6964.260000000001</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.02255735838115748</v>
+        <v>0.02285592194526734</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>771.413235102485</v>
+        <v>729.0450044956448</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
@@ -19967,27 +19897,27 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Provence Area</t>
+          <t>Santiago de Chile Area</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>9593764</v>
+        <v>9471457</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>16</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>-16409.68</v>
+        <v>-331.1300000000001</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.0313384819555703</v>
+        <v>0.05827783412837117</v>
       </c>
       <c r="G66" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -20002,32 +19932,32 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Santiago de Chile Area</t>
+          <t>Cozumel</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>9533055</v>
+        <v>9449880</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>-331.1300000000001</v>
+        <v>16240.58</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.05792235542541189</v>
+        <v>0.03792915888879012</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1718.601717693769</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20037,32 +19967,32 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Cozumel</t>
+          <t>Provence Area</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>9449880</v>
+        <v>9111547</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>16240.58</v>
+        <v>-16596.32</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>0.03792915888879012</v>
+        <v>0.03178000398834577</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>1718.601717693769</v>
+        <v>0</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20072,32 +20002,32 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Medellin Area</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>9392419</v>
+        <v>8929749</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>8681.560000000001</v>
+        <v>410.78</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.02692416085781522</v>
+        <v>0.05526034382377377</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>924.3156635154374</v>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>46.00129298147126</v>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20107,32 +20037,32 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Medellin Area</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>9229557</v>
+        <v>8908302</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>410.78</v>
+        <v>8861.280000000001</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.05571014946871231</v>
+        <v>0.025732064314838</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>44.50701154995846</v>
-      </c>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>994.721552996295</v>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20142,27 +20072,27 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Detroit Area</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>9108008</v>
+        <v>8789215</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>12716.06</v>
+        <v>29135.47</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0.01824218863224538</v>
+        <v>0.1231434206581589</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>1396.140627017455</v>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>3314.911513713113</v>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -20177,27 +20107,27 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Edinburgh Area</t>
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>8854150</v>
+        <v>8549919</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="E72" s="13" t="n">
-        <v>29135.47</v>
+        <v>49814.79</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>0.1223761738845626</v>
+        <v>0.02174488436674078</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>3290.60045289497</v>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>5826.346425036308</v>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -20212,32 +20142,32 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>San Andres, Providencia y Santa Catalina</t>
+          <t>Vienna Area</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>8845681</v>
+        <v>8461708</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>30128.6</v>
+        <v>3888.609999999999</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.02374141685642971</v>
+        <v>0.02088360884114649</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>3406.023798506865</v>
+        <v>459.5537922131087</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -20251,19 +20181,19 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>8777449</v>
+        <v>8410139</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>23183.64</v>
+        <v>22432.27</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>0.04749181681374623</v>
+        <v>0.04802381982033829</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>2641.273107938309</v>
+        <v>2667.288852181872</v>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
@@ -20282,23 +20212,23 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>San Andres, Providencia y Santa Catalina</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>8645920</v>
+        <v>8360062</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>12207.76</v>
+        <v>29624</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.02823111941817643</v>
+        <v>0.0238273352518199</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>1411.967725817495</v>
+        <v>3543.514390204284</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
@@ -20317,32 +20247,32 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Vienna Area</t>
+          <t>Hawái</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>8640332</v>
+        <v>8064785</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>3100.149999999999</v>
+        <v>9198.5</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.02085128210351176</v>
+        <v>0.02593261940646899</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>358.7998701901731</v>
+        <v>1140.575973197054</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20352,27 +20282,27 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Edinburgh Area</t>
+          <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>8549919</v>
+        <v>8001625</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>109</v>
+        <v>373</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>49814.79</v>
+        <v>154434.27</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.02174488436674078</v>
+        <v>0.03107593770015465</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>5826.346425036308</v>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>19300.36336369175</v>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -20387,23 +20317,23 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Columbus (and vicinity), OH, US</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>8468714</v>
+        <v>7915071</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>9611.91</v>
+        <v>11815.45</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.01935594943931275</v>
+        <v>0.02749994283058231</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>1134.990507413522</v>
+        <v>1492.778776084257</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
@@ -20422,27 +20352,27 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Indianápolis Area</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>8199005</v>
+        <v>7500696</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>12660.08</v>
+        <v>5022.32</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.01913707821863751</v>
+        <v>0.03362847927712308</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>1544.099558422028</v>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>669.5805295935203</v>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -20457,23 +20387,23 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Hawái</t>
+          <t>Detroit Area</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>8193142</v>
+        <v>7443847</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>9198.5</v>
+        <v>11310.09</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>0.02586760976436146</v>
+        <v>0.02055764982810636</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>1122.707259315169</v>
+        <v>1519.387757432414</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
@@ -20496,7 +20426,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>8069685</v>
+        <v>7226988</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>78</v>
@@ -20505,10 +20435,10 @@
         <v>10203.52</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>0.01712433632787401</v>
+        <v>0.01738552769148088</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>1264.426058761897</v>
+        <v>1411.863420833133</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
@@ -20527,27 +20457,27 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Ixtapa / Zihuatanejo</t>
+          <t>Pittsburgh Area</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>8067500</v>
+        <v>7050431</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>373</v>
+        <v>70</v>
       </c>
       <c r="E82" s="13" t="n">
-        <v>154434.27</v>
+        <v>18632.45</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>0.03107530213820886</v>
+        <v>0.02492854692145771</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>19142.76665633715</v>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>2642.739146018166</v>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -20562,32 +20492,32 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Osaka Area</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>7875544</v>
+        <v>7031931</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>5022.32</v>
+        <v>-7844.63</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.03246467799557719</v>
+        <v>0.06612067154811388</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>637.7108679730568</v>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0</v>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20597,32 +20527,32 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Birmingham Area</t>
+          <t>San Jose Area</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>7670777</v>
+        <v>6987594</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>7789.27</v>
+        <v>3815.89</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0.007356751473807673</v>
+        <v>0.01556344000524358</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>1015.447326913558</v>
+        <v>546.0949791873999</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20632,32 +20562,32 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Charlotte Area</t>
+          <t>Paris Area</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>7611046</v>
+        <v>6881775</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>6493.37</v>
+        <v>-28.97</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>0.01258263318865764</v>
+        <v>0.02037032596968079</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>853.150802136789</v>
+        <v>0</v>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20667,32 +20597,32 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>San Jose Area</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>7484337</v>
+        <v>6718172</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>3815.89</v>
+        <v>17292.29</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>0.01646919426530366</v>
+        <v>0.01469358033703216</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>509.850104291135</v>
+        <v>2573.957618233055</v>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20702,23 +20632,23 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Pittsburgh Area</t>
+          <t>Columbus (and vicinity), OH, US</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>7416996</v>
+        <v>6709034</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>18632.45</v>
+        <v>10296.26</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.02376824795375378</v>
+        <v>0.02084607113334051</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>2512.128899624592</v>
+        <v>1534.685917525534</v>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
@@ -20737,32 +20667,32 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Osaka Area</t>
+          <t>Birmingham Area</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>7213838</v>
+        <v>6695511</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>-7539.8</v>
+        <v>7478.09</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>0.06692456914058785</v>
+        <v>0.007231262856561657</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1116.881146188842</v>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20772,32 +20702,32 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Charleston Area</t>
+          <t>Bayahibe</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>7154728</v>
+        <v>6539063</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>4634.6</v>
+        <v>7210.660000000001</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.01394434561313861</v>
+        <v>0.1819000673338061</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>647.767462299056</v>
-      </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1102.705387606757</v>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20807,27 +20737,27 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Merida</t>
+          <t>Indianápolis Area</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>7149134</v>
+        <v>6531031</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E90" s="13" t="n">
-        <v>12482.29</v>
+        <v>10326.05</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>0.03839276197648554</v>
+        <v>0.01961543284666694</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>1745.986297081577</v>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1581.075024754897</v>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -20842,20 +20772,20 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Paris Area</t>
+          <t>Manchester Area</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>7038005</v>
+        <v>6510080</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>-28.97</v>
+        <v>-422.58</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.02019421696915532</v>
+        <v>0.006322656557215887</v>
       </c>
       <c r="G91" s="13" t="n">
         <v>0</v>
@@ -20877,27 +20807,27 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Jacksonville Area</t>
+          <t>Merida</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>7035175</v>
+        <v>6433541</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>5250.76</v>
+        <v>12482.29</v>
       </c>
       <c r="F92" s="14" t="n">
-        <v>0.01685473353541312</v>
+        <v>0.03906309138311235</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>746.3581218661938</v>
-      </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1940.189702684727</v>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -20912,32 +20842,32 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Manchester Area</t>
+          <t>Charleston Area</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>6998672</v>
+        <v>6422731</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>25.99000000000002</v>
+        <v>4634.6</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0.006386640208313806</v>
+        <v>0.01508392613671661</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>3.713561658554655</v>
+        <v>721.5933533570067</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20947,27 +20877,27 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Niagara Falls, Canada</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>6718172</v>
+        <v>6365487</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>17292.29</v>
+        <v>7128.11</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>0.01469358033703216</v>
+        <v>0.0423103526878619</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>2573.957618233055</v>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1119.805915871009</v>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -20982,23 +20912,23 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Niagara Falls, Canada</t>
+          <t>Ottawa Area</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>6544616</v>
+        <v>6238426</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>7269.09</v>
+        <v>8248.93</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>0.04145208825086147</v>
+        <v>0.0405813902417052</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>1110.697709384324</v>
+        <v>1322.277446266093</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
@@ -21017,27 +20947,27 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Bayahibe</t>
+          <t>Huatulco Area</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>6539063</v>
+        <v>5988635</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="E96" s="13" t="n">
-        <v>7210.660000000001</v>
+        <v>89450.36</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>0.1819000673338061</v>
+        <v>0.03840507895371817</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>1102.705387606757</v>
-      </c>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>14936.68590588673</v>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -21052,23 +20982,23 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Orange County Area</t>
+          <t>Jacksonville Area</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>6526239</v>
+        <v>5972035</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>14559.77</v>
+        <v>5041.1</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>0.02092843979511017</v>
+        <v>0.0173764889187689</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>2230.958749748515</v>
+        <v>844.1176248967062</v>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
@@ -21087,32 +21017,32 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Ottawa Area</t>
+          <t>El Cairo Area</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>6502063</v>
+        <v>5971938</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="E98" s="13" t="n">
-        <v>8248.93</v>
+        <v>274.42</v>
       </c>
       <c r="F98" s="14" t="n">
-        <v>0.04036764946756129</v>
+        <v>0.02184282556181929</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>1268.663499569291</v>
-      </c>
-      <c r="H98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>45.95158221669414</v>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -21122,32 +21052,32 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Huatulco Area</t>
+          <t>Fráncfort</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>6227289</v>
+        <v>5853082</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>89369.52</v>
+        <v>2978.2</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0.0373234645124066</v>
+        <v>0.0196050559346341</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>14351.27227915711</v>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
+        <v>508.8259484490393</v>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21157,32 +21087,32 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Fráncfort</t>
+          <t>Charlotte Area</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>6213402</v>
+        <v>5721789</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>2978.2</v>
+        <v>6150.02</v>
       </c>
       <c r="F100" s="14" t="n">
-        <v>0.01924082813247879</v>
+        <v>0.01089082453057951</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>479.3187371427118</v>
+        <v>1074.842151641733</v>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21192,23 +21122,23 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>San Jose - Silicon Valley Area</t>
+          <t>Orange County Area</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>6044145</v>
+        <v>5680022</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>10343.58</v>
+        <v>14559.77</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>0.01848168764978339</v>
+        <v>0.01841418924081632</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>1711.33882459802</v>
+        <v>2563.32986034209</v>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
@@ -21227,23 +21157,23 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Savannah Area</t>
+          <t>Hamburg Area</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>6038536</v>
+        <v>5675717</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E102" s="13" t="n">
-        <v>5112.17</v>
+        <v>6421.340000000001</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>0.02085720777353981</v>
+        <v>0.01913079880480299</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>846.5909617827897</v>
+        <v>1131.370714924652</v>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
@@ -21262,32 +21192,32 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>El Cairo Area</t>
+          <t>West Palm Beach Area</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>6032013</v>
+        <v>5486502</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>274.42</v>
+        <v>6944.58</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>0.02419258711809805</v>
+        <v>0.01065068416998663</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>45.49393378296764</v>
+        <v>1265.757307661603</v>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21301,7 +21231,7 @@
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>5907598</v>
+        <v>5413163</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>27</v>
@@ -21310,10 +21240,10 @@
         <v>8917.969999999999</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.01199573836946928</v>
+        <v>0.01196250694834055</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>1509.576311726018</v>
+        <v>1647.460089415375</v>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
@@ -21332,32 +21262,32 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Hamburg Area</t>
+          <t>Colonia Area</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>5859891</v>
+        <v>5401309</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>6421.340000000001</v>
+        <v>3286.01</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>0.02046693359995945</v>
+        <v>0.01628549671940635</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>1095.812191728481</v>
+        <v>608.3728962738476</v>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21372,7 +21302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -21403,7 +21333,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21464,19 +21394,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>1655580862</v>
+        <v>1481061235</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>8281</v>
+        <v>7392</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>1605650.82</v>
+        <v>1478967.61</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.02639582457314006</v>
+        <v>0.02827172098660728</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>969.8413752260444</v>
+        <v>998.5864021348179</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -21499,19 +21429,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>538292976</v>
+        <v>527455823</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>5578</v>
+        <v>5500</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1962355.19</v>
+        <v>1947393.3</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.03824285829061236</v>
+        <v>0.03830351115490482</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>3645.515133008164</v>
+        <v>3692.050054398584</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -21534,19 +21464,19 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>148710044</v>
+        <v>142083016</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>139106.71</v>
+        <v>137719.3</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.01879828641567748</v>
+        <v>0.01928837152499634</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>935.4224251322257</v>
+        <v>969.2875607313965</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -21565,27 +21495,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>137053314</v>
+        <v>128335643</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>623</v>
+        <v>979</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>118137.29</v>
+        <v>576163.05</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.03132440124724018</v>
+        <v>0.05133465533032004</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>861.98054284189</v>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>4489.501408427899</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -21600,27 +21530,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>128573023</v>
+        <v>125594155</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>979</v>
+        <v>588</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>576163.05</v>
+        <v>109439.49</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.05125543326456593</v>
+        <v>0.03316456088263025</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>4481.212594651368</v>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>871.374069915913</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -21639,19 +21569,19 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>125750026</v>
+        <v>120411294</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>32577.05</v>
+        <v>31695.55999999999</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.03548998868596655</v>
+        <v>0.03624490573118498</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>259.0619742694924</v>
+        <v>263.227467682558</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
@@ -21674,19 +21604,19 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>85351532</v>
+        <v>81558552</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>94889.50999999999</v>
+        <v>94460.05</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.01691986032541279</v>
+        <v>0.01664824799734061</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1111.749347393085</v>
+        <v>1158.186942799083</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
@@ -21709,19 +21639,19 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>75968554</v>
+        <v>72952941</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>83957.72</v>
+        <v>82320.97</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.01641088232375728</v>
+        <v>0.01628542980878591</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1105.164118300843</v>
+        <v>1128.411944351908</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -21744,28 +21674,28 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>58661241</v>
+        <v>56291592</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>40547.56</v>
+        <v>36105.55</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.1126537196852007</v>
+        <v>0.1109505128225899</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>691.2155165622903</v>
+        <v>641.4021831182177</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21779,7 +21709,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>53598637</v>
+        <v>51432402</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>88</v>
@@ -21788,10 +21718,10 @@
         <v>16661.86</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.05733433109502393</v>
+        <v>0.05617460759464433</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>310.8635019953959</v>
+        <v>323.9564817524953</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
@@ -21814,19 +21744,19 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>46001335</v>
+        <v>44857635</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>13996.09</v>
+        <v>13878.12</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.07644571619497564</v>
+        <v>0.07590382328448658</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>304.2539961068521</v>
+        <v>309.3814464360415</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -21849,28 +21779,28 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>42383275</v>
+        <v>41059019</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>8555.08</v>
+        <v>7919.41</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0.08285284702515321</v>
+        <v>0.08270389996409802</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>201.8503761212412</v>
+        <v>192.878694934236</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -21884,7 +21814,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>35597037</v>
+        <v>34558758</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>19</v>
@@ -21893,10 +21823,10 @@
         <v>7084.5</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.05901814243696744</v>
+        <v>0.05641386186390147</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>199.0193734383005</v>
+        <v>204.9986865847436</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
@@ -21919,19 +21849,19 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>27728510</v>
+        <v>26232503</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>9973.57</v>
+        <v>9959.719999999999</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.06459845840977391</v>
+        <v>0.06599553233635387</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>359.6864743183099</v>
+        <v>379.6709753545058</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
@@ -21954,7 +21884,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>17264080</v>
+        <v>16786254</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>30</v>
@@ -21963,7 +21893,7 @@
         <v>-3986.71</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.02282224132418293</v>
+        <v>0.0224430060453035</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>0</v>
@@ -21989,28 +21919,28 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>12010640</v>
+        <v>11764195</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>8808.300000000001</v>
+        <v>7201.250000000002</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.04038077904258224</v>
+        <v>0.04058076221959939</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>733.3747410629243</v>
+        <v>612.1328318682241</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22024,19 +21954,19 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>11919785</v>
+        <v>11740825</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>9324.959999999999</v>
+        <v>9126.450000000001</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.02627220205733576</v>
+        <v>0.02618563857309856</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>782.3094124600401</v>
+        <v>777.326124867716</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
@@ -22059,7 +21989,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>11793810</v>
+        <v>11127961</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>10</v>
@@ -22068,10 +21998,10 @@
         <v>410.78</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.05461805811692744</v>
+        <v>0.05385883361740754</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>34.8301354693691</v>
+        <v>36.91421995458108</v>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
@@ -22090,32 +22020,32 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>11088941</v>
+        <v>10833685</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>715.3000000000001</v>
+        <v>37983.31</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.04488679306707467</v>
+        <v>0.07126531738738942</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>64.50570888599732</v>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>3506.037880924173</v>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22125,32 +22055,32 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>11057435</v>
+        <v>10610124</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>22462.44</v>
+        <v>715.3000000000001</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.04183411433121696</v>
+        <v>0.03866184787284296</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>2031.433148827011</v>
+        <v>67.41674272609822</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22160,27 +22090,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>10889277</v>
+        <v>10316370</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>37983.31</v>
+        <v>22062.69</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.07094979767710932</v>
+        <v>0.04294640459774126</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>3488.138836031079</v>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>2138.609801703506</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -22199,19 +22129,19 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>10640667</v>
+        <v>10169344</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2910.699999999999</v>
+        <v>4443.83</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.0204474963834504</v>
+        <v>0.02019294459898298</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>273.5448821018456</v>
+        <v>436.982955832746</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
@@ -22234,28 +22164,28 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>10560065</v>
+        <v>10050101</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>1945.25</v>
+        <v>2800.41</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.005155271298045988</v>
+        <v>0.004763136211267926</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>184.2081464460683</v>
+        <v>278.6449608814876</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22265,32 +22195,32 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>10093581</v>
+        <v>9777961</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>19068</v>
+        <v>-331.1300000000001</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.05794038805454674</v>
+        <v>0.05688200229066162</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>1889.121412905885</v>
+        <v>0</v>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22300,32 +22230,32 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>9894441</v>
+        <v>9523621</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>-168.7300000000002</v>
+        <v>14775.12</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.05633314706712587</v>
+        <v>0.05766882155432267</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0</v>
+        <v>1551.418310325453</v>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22339,7 +22269,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>8854150</v>
+        <v>8789215</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>68</v>
@@ -22348,10 +22278,10 @@
         <v>29135.47</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.1223761738845626</v>
+        <v>0.1231434206581589</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>3290.60045289497</v>
+        <v>3314.911513713113</v>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
@@ -22374,7 +22304,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>8154366</v>
+        <v>8027816</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>14</v>
@@ -22383,10 +22313,10 @@
         <v>2226.46</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.03733926095541946</v>
+        <v>0.03784765370805709</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>273.0390075696872</v>
+        <v>277.3431777708906</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -22405,32 +22335,32 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>6930674</v>
+        <v>6718172</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>2004.6</v>
+        <v>17292.29</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.06066870263988755</v>
+        <v>0.01469358033703216</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>289.2359386691684</v>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>2573.957618233055</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22440,32 +22370,32 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>6832952</v>
+        <v>6437233</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>1273.24</v>
+        <v>2004.6</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0.03398750642474878</v>
+        <v>0.05882232319383188</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>186.3382034587686</v>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>311.4070905931167</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22475,32 +22405,32 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>6718172</v>
+        <v>6123703</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>17292.29</v>
+        <v>1273.24</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.01469358033703216</v>
+        <v>0.03174435468212616</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>2573.957618233055</v>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>207.9199464768294</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22510,32 +22440,32 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>6351607</v>
+        <v>5949475</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>-7313.420000000001</v>
+        <v>6714.180000000001</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.0155862917841107</v>
+        <v>0.09562440383395174</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1128.533189903311</v>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22545,32 +22475,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Grecia</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>6125380</v>
+        <v>5818121</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>6714.180000000001</v>
+        <v>-7958.830000000001</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.0969739020273028</v>
+        <v>0.01406450639304339</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1096.12464859323</v>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22514,7 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>4714377</v>
+        <v>4589294</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>23</v>
@@ -22593,10 +22523,10 @@
         <v>2807.71</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.04595071628764522</v>
+        <v>0.04563272695102994</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>595.5633162133619</v>
+        <v>611.7956269526425</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
@@ -22619,7 +22549,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>4416271</v>
+        <v>4297294</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>55</v>
@@ -22628,10 +22558,10 @@
         <v>7882.089999999999</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.02209964017153838</v>
+        <v>0.01724108241139657</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>1784.784040653302</v>
+        <v>1834.198451397554</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -22654,7 +22584,7 @@
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>4115439</v>
+        <v>3819448</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>0</v>
@@ -22663,7 +22593,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.2050068048633451</v>
+        <v>0.2025132951148962</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>0</v>
@@ -22689,7 +22619,7 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>3904722</v>
+        <v>3779363</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>5</v>
@@ -22698,10 +22628,10 @@
         <v>5299.98</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.04888721911572706</v>
+        <v>0.04996371081581737</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>1357.325822427307</v>
+        <v>1402.347432622905</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -22724,7 +22654,7 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>3484243</v>
+        <v>3187780</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>13</v>
@@ -22733,10 +22663,10 @@
         <v>1165.29</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.01409201367413237</v>
+        <v>0.01054307386331553</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>334.4456744262671</v>
+        <v>365.5490654938547</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
@@ -22759,7 +22689,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>2873706</v>
+        <v>2818728</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>9</v>
@@ -22768,10 +22698,10 @@
         <v>1134.62</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.03016940494260721</v>
+        <v>0.03014054566456927</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>394.8281417792912</v>
+        <v>402.5290840407446</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
@@ -22794,7 +22724,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>2600590</v>
+        <v>2539437</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>14</v>
@@ -22803,10 +22733,10 @@
         <v>2646.84</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.02603024698241553</v>
+        <v>0.02322758942237984</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>1017.784425841828</v>
+        <v>1042.294020288749</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -22825,27 +22755,27 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Nueva Zelanda (Aotearoa)</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>2247022</v>
+        <v>2108715</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>444.15</v>
+        <v>-2157.87</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.01069860464205513</v>
+        <v>0.1155722798007317</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>197.6616161301492</v>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -22860,32 +22790,32 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>2108715</v>
+        <v>2107870</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>-2157.87</v>
+        <v>0</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.1155722798007317</v>
+        <v>0.02530848676626168</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22895,32 +22825,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Nueva Zelanda (Aotearoa)</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>2107870</v>
+        <v>1952227</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>0</v>
+        <v>444.15</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.02530848676626168</v>
+        <v>0.004830380893205554</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0</v>
+        <v>227.5094033634408</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22930,27 +22860,27 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Mauricio</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1952862</v>
+        <v>1779898</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>-660.64</v>
+        <v>-828.65</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.1498605636240554</v>
+        <v>0.02961967483529955</v>
       </c>
       <c r="G48" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -22965,27 +22895,27 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Mauricio</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>1779898</v>
+        <v>1720097</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>-828.65</v>
+        <v>-660.64</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.02961967483529955</v>
+        <v>0.1169091045446856</v>
       </c>
       <c r="G49" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -23004,7 +22934,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1761075</v>
+        <v>1698554</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>2</v>
@@ -23013,10 +22943,10 @@
         <v>131.21</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.02184006927586843</v>
+        <v>0.01826141529795344</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>74.50562866431015</v>
+        <v>77.24805923155814</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
@@ -23070,32 +23000,32 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Islas Caimán</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1310481</v>
+        <v>1258821</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>5314.42</v>
+        <v>0</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0.005427778044855286</v>
+        <v>0.009925160129994655</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>4055.320145809058</v>
+        <v>0</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23105,32 +23035,32 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Islas Caimán</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1279530</v>
+        <v>1243623</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>109.81</v>
+        <v>5314.42</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.01963299023860324</v>
+        <v>0.005547501131773857</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>85.82057474228819</v>
+        <v>4273.336855301003</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23140,32 +23070,32 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>1258821</v>
+        <v>1155943</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>0</v>
+        <v>109.81</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.009925160129994655</v>
+        <v>0.02090241473844298</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0</v>
+        <v>94.99603354144625</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23175,32 +23105,32 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Malasia</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1220756</v>
+        <v>1150608</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.1466435553050733</v>
+        <v>0.02190754800940024</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23210,20 +23140,20 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1210595</v>
+        <v>1124247</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>0</v>
+        <v>-371.8199999999999</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0.02260623908078259</v>
+        <v>0.004587959763290453</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>0</v>
@@ -23245,32 +23175,32 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Finlandia</t>
+          <t>Malasia</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1124247</v>
+        <v>983336</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>-371.8199999999999</v>
+        <v>0</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.004587959763290453</v>
+        <v>0.1417806324593018</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23284,28 +23214,28 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>962534</v>
+        <v>901892</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>707.8900000000001</v>
+        <v>505.4900000000001</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.0134447198748304</v>
+        <v>0.01332642932856706</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>735.4441505442926</v>
+        <v>560.4773077042486</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -23315,27 +23245,27 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>957325</v>
+        <v>890387</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>2419.36</v>
+        <v>946.5899999999999</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.0329271668451153</v>
+        <v>0.02311242190193702</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>2527.208628208811</v>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1063.121990774798</v>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -23350,32 +23280,32 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Singapur</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>945399</v>
+        <v>804747</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>946.5899999999999</v>
+        <v>0</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.02192513425548366</v>
+        <v>0.1112548415837524</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>1001.259785550863</v>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23385,11 +23315,11 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Åland</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>870425</v>
+        <v>803773</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>0</v>
@@ -23398,14 +23328,14 @@
         <v>0</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.1064008961139673</v>
+        <v>0.007865404784684234</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -23420,32 +23350,32 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>833854</v>
+        <v>772825</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>62.13</v>
+        <v>2264.62</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0.01357311951492708</v>
+        <v>0.02682625432665869</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>74.50944649782815</v>
+        <v>2930.314107333484</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23455,32 +23385,32 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Åland</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>803773</v>
+        <v>771962</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>0</v>
+        <v>62.13</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.007865404784684234</v>
+        <v>0.0133309670683272</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0</v>
+        <v>80.48323622147204</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23525,32 +23455,32 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>695408</v>
+        <v>645251</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>1315.1</v>
+        <v>-2355.61</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.04414962151715252</v>
+        <v>0.03256252218129069</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>1891.120033131629</v>
+        <v>0</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23560,32 +23490,32 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>657844</v>
+        <v>633423</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>970.5899999999999</v>
+        <v>0</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.008848602404217415</v>
+        <v>0.01190673530957985</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>1475.410583664212</v>
+        <v>0</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23595,32 +23525,32 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>645251</v>
+        <v>598831</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>-2355.61</v>
+        <v>970.5899999999999</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.03256252218129069</v>
+        <v>0.008182609116762496</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1620.807874007858</v>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23630,32 +23560,32 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Corea (Sur)</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>643720</v>
+        <v>581554</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>0</v>
+        <v>928.84</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>0.1512753992419064</v>
+        <v>0.03521255119902881</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>1597.168964532958</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23665,20 +23595,20 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Lituania</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>633423</v>
+        <v>558377</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>0</v>
+        <v>-2235.07</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.01190673530957985</v>
+        <v>0.009103168647705762</v>
       </c>
       <c r="G69" s="13" t="n">
         <v>0</v>
@@ -23688,9 +23618,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23700,20 +23630,20 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>623147</v>
+        <v>527811</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>-2235.07</v>
+        <v>0</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.01133119472612401</v>
+        <v>0.004863483330207214</v>
       </c>
       <c r="G70" s="13" t="n">
         <v>0</v>
@@ -23723,9 +23653,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23735,11 +23665,11 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Corea (Sur)</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>586274</v>
+        <v>519667</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>0</v>
@@ -23748,14 +23678,14 @@
         <v>0</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0.006882447456308825</v>
+        <v>0.1583360113303327</v>
       </c>
       <c r="G71" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
@@ -23770,11 +23700,11 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Polonia</t>
+          <t>Uzbekistán</t>
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>567593</v>
+        <v>513571</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>0</v>
@@ -23783,14 +23713,14 @@
         <v>0</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>0.09400750185432168</v>
+        <v>0.003939085345551053</v>
       </c>
       <c r="G72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -23805,11 +23735,11 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Uzbekistán</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>513571</v>
+        <v>496895</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>0</v>
@@ -23818,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.003939085345551053</v>
+        <v>0.007629378440113102</v>
       </c>
       <c r="G73" s="13" t="n">
         <v>0</v>
@@ -23840,32 +23770,32 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>496895</v>
+        <v>466906</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>0</v>
+        <v>1003.49</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>0.007629378440113102</v>
+        <v>0.0420577161141643</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>2149.233464551751</v>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23875,32 +23805,32 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Eslovaquia</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>466906</v>
+        <v>453415</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>1003.49</v>
+        <v>0</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.0420577161141643</v>
+        <v>0.003546419946406713</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>2149.233464551751</v>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23910,11 +23840,11 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Eslovenia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>453415</v>
+        <v>384063</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>0</v>
@@ -23923,14 +23853,14 @@
         <v>0</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.003546419946406713</v>
+        <v>0.07559436863222961</v>
       </c>
       <c r="G76" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -23945,11 +23875,11 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Camboya</t>
+          <t>Bangladés</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>426074</v>
+        <v>383943</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>0</v>
@@ -23958,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.00132606073123448</v>
+        <v>0.001341344939222749</v>
       </c>
       <c r="G77" s="13" t="n">
         <v>0</v>
@@ -23980,11 +23910,11 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Santa Lucía</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>399911</v>
+        <v>372809</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>0</v>
@@ -23993,14 +23923,14 @@
         <v>0</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.06617722443243622</v>
+        <v>0.004361482689527345</v>
       </c>
       <c r="G78" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -24015,11 +23945,11 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Belice</t>
+          <t>Camboya</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>391685</v>
+        <v>361395</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>0</v>
@@ -24028,7 +23958,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.01022760636736153</v>
+        <v>0.001209203226386641</v>
       </c>
       <c r="G79" s="13" t="n">
         <v>0</v>
@@ -24050,11 +23980,11 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Bangladés</t>
+          <t>Kirguistán</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>383943</v>
+        <v>359819</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>0</v>
@@ -24063,7 +23993,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>0.001341344939222749</v>
+        <v>0.00311545527056659</v>
       </c>
       <c r="G80" s="13" t="n">
         <v>0</v>
@@ -24085,11 +24015,11 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Letonia</t>
+          <t>Santa Lucía</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>372809</v>
+        <v>335826</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>0</v>
@@ -24098,14 +24028,14 @@
         <v>0</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>0.004361482689527345</v>
+        <v>0.07806721337835665</v>
       </c>
       <c r="G81" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -24120,11 +24050,11 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Kirguistán</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>359819</v>
+        <v>331129</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>0</v>
@@ -24133,14 +24063,14 @@
         <v>0</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>0.00311545527056659</v>
+        <v>0.05001374086836248</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -24155,11 +24085,11 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>331129</v>
+        <v>304706</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>0</v>
@@ -24168,14 +24098,14 @@
         <v>0</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.05001374086836248</v>
+        <v>0.04101330462806771</v>
       </c>
       <c r="G83" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -24190,11 +24120,11 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Dinamarca</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>321520</v>
+        <v>300840</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>0</v>
@@ -24203,14 +24133,14 @@
         <v>0</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0.1704963921373476</v>
+        <v>0.3034636351548996</v>
       </c>
       <c r="G84" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -24225,11 +24155,11 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Belice</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>304706</v>
+        <v>272155</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>0</v>
@@ -24238,14 +24168,14 @@
         <v>0</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>0.04101330462806771</v>
+        <v>0.00504859363230512</v>
       </c>
       <c r="G85" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -24260,11 +24190,11 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>300840</v>
+        <v>262183</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>0</v>
@@ -24273,14 +24203,14 @@
         <v>0</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>0.3034636351548996</v>
+        <v>0.1946045319490585</v>
       </c>
       <c r="G86" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -24295,11 +24225,11 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Hong kong</t>
+          <t>Bermudas</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>286021</v>
+        <v>235955</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>0</v>
@@ -24308,14 +24238,14 @@
         <v>0</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.1769275682554778</v>
+        <v>0.005768048992392617</v>
       </c>
       <c r="G87" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -24330,11 +24260,11 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Bermudas</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>235955</v>
+        <v>201257</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>0</v>
@@ -24343,14 +24273,14 @@
         <v>0</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>0.005768048992392617</v>
+        <v>0.03131319655962277</v>
       </c>
       <c r="G88" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -24365,11 +24295,11 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Fiyi</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>201257</v>
+        <v>201190</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>0</v>
@@ -24378,7 +24308,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.03131319655962277</v>
+        <v>0.03366469506436701</v>
       </c>
       <c r="G89" s="13" t="n">
         <v>0</v>
@@ -24400,32 +24330,32 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Fiyi</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>201190</v>
+        <v>183139</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E90" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>0.03366469506436701</v>
+        <v>0.001244956017014399</v>
       </c>
       <c r="G90" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -24435,20 +24365,20 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>183139</v>
+        <v>177771</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E91" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.001244956017014399</v>
+        <v>0.01906385180935023</v>
       </c>
       <c r="G91" s="13" t="n">
         <v>0</v>
@@ -24458,9 +24388,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24470,32 +24400,32 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>177771</v>
+        <v>176361</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>0</v>
+        <v>1938.78</v>
       </c>
       <c r="F92" s="14" t="n">
-        <v>0.01906385180935023</v>
+        <v>0.0005329976582124165</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0</v>
+        <v>10993.24680626669</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24505,23 +24435,23 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>176361</v>
+        <v>174792</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>1938.78</v>
+        <v>695.52</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0.0005329976582124165</v>
+        <v>0.001247196668039727</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>10993.24680626669</v>
+        <v>3979.129479610051</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
@@ -24540,32 +24470,32 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Kazajistán</t>
+          <t>Hong kong</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>174792</v>
+        <v>174299</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>695.52</v>
+        <v>0</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>0.001247196668039727</v>
+        <v>0.1317334006506062</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>3979.129479610051</v>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24715,11 +24645,11 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Filipinas</t>
+          <t>Antigua y Barbuda</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>161037</v>
+        <v>160628</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>0</v>
@@ -24728,14 +24658,14 @@
         <v>0</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0.06740065947577265</v>
+        <v>0.03027492093532884</v>
       </c>
       <c r="G99" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
@@ -24750,11 +24680,11 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Antigua y Barbuda</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>160628</v>
+        <v>145683</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>0</v>
@@ -24763,7 +24693,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="14" t="n">
-        <v>0.03027492093532884</v>
+        <v>0.03203530954195068</v>
       </c>
       <c r="G100" s="13" t="n">
         <v>0</v>
@@ -24785,32 +24715,32 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Kenia</t>
+          <t>Anguila</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>156199</v>
+        <v>133615</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>139.06</v>
+        <v>0</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>0.02378376302024981</v>
+        <v>0.001601616584964263</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>890.2745856247479</v>
+        <v>0</v>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24820,11 +24750,11 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Polinesia Francesa</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>153260</v>
+        <v>121660</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>0</v>
@@ -24833,7 +24763,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>0.00525903693070599</v>
+        <v>0.01209929311195134</v>
       </c>
       <c r="G102" s="13" t="n">
         <v>0</v>
@@ -24855,11 +24785,11 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Filipinas</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>145683</v>
+        <v>102267</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>0</v>
@@ -24868,14 +24798,14 @@
         <v>0</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>0.03203530954195068</v>
+        <v>0.09911310588948537</v>
       </c>
       <c r="G103" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -24890,11 +24820,11 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Anguila</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>133615</v>
+        <v>95513</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>0</v>
@@ -24903,14 +24833,14 @@
         <v>0</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.001601616584964263</v>
+        <v>0.1455613372001717</v>
       </c>
       <c r="G104" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -24925,11 +24855,11 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Sint Maarten</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>127971</v>
+        <v>93945</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>0</v>
@@ -24938,7 +24868,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>0.02023896038946324</v>
+        <v>0.003235935919953164</v>
       </c>
       <c r="G105" s="13" t="n">
         <v>0</v>
@@ -24960,11 +24890,11 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Polinesia Francesa</t>
+          <t>Islas Turcas y Caicos</t>
         </is>
       </c>
       <c r="C106" s="12" t="n">
-        <v>121660</v>
+        <v>92758</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>0</v>
@@ -24973,7 +24903,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="14" t="n">
-        <v>0.01209929311195134</v>
+        <v>0.01125509390025658</v>
       </c>
       <c r="G106" s="13" t="n">
         <v>0</v>
@@ -24995,32 +24925,32 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Kenia</t>
         </is>
       </c>
       <c r="C107" s="12" t="n">
-        <v>112015</v>
+        <v>92427</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>0</v>
+        <v>139.06</v>
       </c>
       <c r="F107" s="14" t="n">
-        <v>0.02586260768647056</v>
+        <v>0.03679660705205189</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I107" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>1504.538717041557</v>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -25030,11 +24960,11 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="C108" s="12" t="n">
-        <v>95513</v>
+        <v>87954</v>
       </c>
       <c r="D108" s="5" t="n">
         <v>0</v>
@@ -25043,14 +24973,14 @@
         <v>0</v>
       </c>
       <c r="F108" s="14" t="n">
-        <v>0.1455613372001717</v>
+        <v>0.006844486890874775</v>
       </c>
       <c r="G108" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H108" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -25065,11 +24995,11 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="C109" s="12" t="n">
-        <v>93945</v>
+        <v>74062</v>
       </c>
       <c r="D109" s="5" t="n">
         <v>0</v>
@@ -25078,7 +25008,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="14" t="n">
-        <v>0.003235935919953164</v>
+        <v>0.02797656017930924</v>
       </c>
       <c r="G109" s="13" t="n">
         <v>0</v>
@@ -25100,32 +25030,32 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Islas Turcas y Caicos</t>
+          <t>San Cristóbal y Nieves</t>
         </is>
       </c>
       <c r="C110" s="12" t="n">
-        <v>92758</v>
+        <v>73158</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>0</v>
+        <v>1320.19</v>
       </c>
       <c r="F110" s="14" t="n">
-        <v>0.01125509390025658</v>
+        <v>0.0007928046146696192</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0</v>
+        <v>18045.73662483939</v>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I110" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -25135,32 +25065,32 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Ucrania</t>
         </is>
       </c>
       <c r="C111" s="12" t="n">
-        <v>74062</v>
+        <v>73025</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>0</v>
+        <v>1402.99</v>
       </c>
       <c r="F111" s="14" t="n">
-        <v>0.02797656017930924</v>
+        <v>0.005532351934269086</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0</v>
+        <v>19212.46148579254</v>
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I111" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -25170,240 +25100,30 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>San Cristóbal y Nieves</t>
+          <t>Islas Vírgenes (Británicas)</t>
         </is>
       </c>
       <c r="C112" s="12" t="n">
-        <v>73158</v>
+        <v>67424</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>1320.19</v>
+        <v>0</v>
       </c>
       <c r="F112" s="14" t="n">
-        <v>0.0007928046146696192</v>
+        <v>0.001957759848125296</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>18045.73662483939</v>
+        <v>0</v>
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Ucrania</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="n">
-        <v>73025</v>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E113" s="13" t="n">
-        <v>1402.99</v>
-      </c>
-      <c r="F113" s="14" t="n">
-        <v>0.005532351934269086</v>
-      </c>
-      <c r="G113" s="13" t="n">
-        <v>19212.46148579254</v>
-      </c>
-      <c r="H113" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>Islas Vírgenes (Británicas)</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="n">
-        <v>67424</v>
-      </c>
-      <c r="D114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="14" t="n">
-        <v>0.001957759848125296</v>
-      </c>
-      <c r="G114" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I114" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>Catar</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="n">
-        <v>66621</v>
-      </c>
-      <c r="D115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="14" t="n">
-        <v>0.2421008390747662</v>
-      </c>
-      <c r="G115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I115" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Marruecos</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>64744</v>
-      </c>
-      <c r="D116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="14" t="n">
-        <v>0.5352619547757321</v>
-      </c>
-      <c r="G116" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I116" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>Islas Marianas del Norte</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="n">
-        <v>58161</v>
-      </c>
-      <c r="D117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="14" t="n">
-        <v>0.007032203710390125</v>
-      </c>
-      <c r="G117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I117" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="n">
-        <v>57764</v>
-      </c>
-      <c r="D118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="14" t="n">
-        <v>0.02112042102347483</v>
-      </c>
-      <c r="G118" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I118" s="11" t="inlineStr">
+      <c r="I112" s="11" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21333,7 +21333,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_CUG_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21333,7 +21333,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
